--- a/Tekken 8 Moveset Editing Data.xlsx
+++ b/Tekken 8 Moveset Editing Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cs\Documents\GitHub\Tekken8Movesets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cSles\Desktop\Modding\Tekken8Movesets_OWN_PROJECTS\extracted_chars\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF69DCCC-EDF1-4DAD-82CD-CE5ABA0D4A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CEE8F6-4CBF-4E42-B52F-2CD2AEC0CF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
+    <comment ref="B82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -329,7 +329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D117" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
+    <comment ref="D118" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -352,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D133" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
+    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -367,7 +367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D152" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
+    <comment ref="D153" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -383,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B153" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
+    <comment ref="B154" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -403,7 +403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B160" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
+    <comment ref="B161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -431,7 +431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B166" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
+    <comment ref="B167" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -448,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B167" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
+    <comment ref="B168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -465,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D170" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
+    <comment ref="D171" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -854,7 +854,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1286">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -5877,6 +5877,15 @@
   </si>
   <si>
     <t>Adds homing move trails to both hands at value 0, duration for entire animation</t>
+  </si>
+  <si>
+    <t>0x81ec</t>
+  </si>
+  <si>
+    <t>Able to block?</t>
+  </si>
+  <si>
+    <t>Setting the value makes the opponent able to block despite of frames.</t>
   </si>
 </sst>
 </file>
@@ -6544,15 +6553,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D257"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="51.140625" customWidth="1"/>
-    <col min="4" max="4" width="68.85546875" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
+    <col min="4" max="4" width="68.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6566,7 +6575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1100</v>
       </c>
@@ -6580,7 +6589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>0</v>
       </c>
@@ -6592,7 +6601,7 @@
       </c>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -6606,7 +6615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -6620,7 +6629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -6632,7 +6641,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -6644,7 +6653,7 @@
       </c>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -6656,7 +6665,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -6668,7 +6677,7 @@
       </c>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -6680,7 +6689,7 @@
       </c>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -6692,7 +6701,7 @@
       </c>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -6704,7 +6713,7 @@
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -6716,7 +6725,7 @@
       </c>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -6728,7 +6737,7 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -6740,7 +6749,7 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -6752,7 +6761,7 @@
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -6764,7 +6773,7 @@
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -6776,7 +6785,7 @@
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -6788,7 +6797,7 @@
       </c>
       <c r="D19" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -6800,7 +6809,7 @@
       </c>
       <c r="D20" s="8"/>
     </row>
-    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>18</v>
       </c>
@@ -6812,7 +6821,7 @@
       </c>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>23</v>
       </c>
@@ -6824,7 +6833,7 @@
       </c>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>24</v>
       </c>
@@ -6836,7 +6845,7 @@
       </c>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>25</v>
       </c>
@@ -6848,7 +6857,7 @@
       </c>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>26</v>
       </c>
@@ -6860,7 +6869,7 @@
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>27</v>
       </c>
@@ -6872,7 +6881,7 @@
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>28</v>
       </c>
@@ -6884,7 +6893,7 @@
       </c>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>29</v>
       </c>
@@ -6896,7 +6905,7 @@
       </c>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>30</v>
       </c>
@@ -6908,7 +6917,7 @@
       </c>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>31</v>
       </c>
@@ -6920,7 +6929,7 @@
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>32</v>
       </c>
@@ -6932,7 +6941,7 @@
       </c>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>33</v>
       </c>
@@ -6944,7 +6953,7 @@
       </c>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>34</v>
       </c>
@@ -6956,7 +6965,7 @@
       </c>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>35</v>
       </c>
@@ -6970,7 +6979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>36</v>
       </c>
@@ -6984,7 +6993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>43</v>
       </c>
@@ -6998,7 +7007,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>44</v>
       </c>
@@ -7012,7 +7021,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>47</v>
       </c>
@@ -7026,7 +7035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>48</v>
       </c>
@@ -7040,7 +7049,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>49</v>
       </c>
@@ -7054,7 +7063,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>50</v>
       </c>
@@ -7066,7 +7075,7 @@
       </c>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>51</v>
       </c>
@@ -7080,7 +7089,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>61</v>
       </c>
@@ -7092,7 +7101,7 @@
       </c>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>62</v>
       </c>
@@ -7106,7 +7115,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>63</v>
       </c>
@@ -7118,7 +7127,7 @@
       </c>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>64</v>
       </c>
@@ -7130,7 +7139,7 @@
       </c>
       <c r="D46" s="8"/>
     </row>
-    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>65</v>
       </c>
@@ -7144,7 +7153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>66</v>
       </c>
@@ -7156,7 +7165,7 @@
       </c>
       <c r="D48" s="8"/>
     </row>
-    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>67</v>
       </c>
@@ -7168,7 +7177,7 @@
       </c>
       <c r="D49" s="8"/>
     </row>
-    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>68</v>
       </c>
@@ -7180,7 +7189,7 @@
       </c>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>69</v>
       </c>
@@ -7192,7 +7201,7 @@
       </c>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>70</v>
       </c>
@@ -7204,7 +7213,7 @@
       </c>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>71</v>
       </c>
@@ -7216,7 +7225,7 @@
       </c>
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>72</v>
       </c>
@@ -7230,7 +7239,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>73</v>
       </c>
@@ -7244,7 +7253,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>76</v>
       </c>
@@ -7256,7 +7265,7 @@
       </c>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>77</v>
       </c>
@@ -7268,7 +7277,7 @@
       </c>
       <c r="D57" s="8"/>
     </row>
-    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>87</v>
       </c>
@@ -7280,7 +7289,7 @@
       </c>
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>92</v>
       </c>
@@ -7292,7 +7301,7 @@
       </c>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>93</v>
       </c>
@@ -7304,7 +7313,7 @@
       </c>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>94</v>
       </c>
@@ -7316,7 +7325,7 @@
       </c>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>95</v>
       </c>
@@ -7328,7 +7337,7 @@
       </c>
       <c r="D62" s="8"/>
     </row>
-    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>96</v>
       </c>
@@ -7340,7 +7349,7 @@
       </c>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>97</v>
       </c>
@@ -7352,7 +7361,7 @@
       </c>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>98</v>
       </c>
@@ -7364,7 +7373,7 @@
       </c>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>99</v>
       </c>
@@ -7376,7 +7385,7 @@
       </c>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>100</v>
       </c>
@@ -7390,7 +7399,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>101</v>
       </c>
@@ -7402,7 +7411,7 @@
       </c>
       <c r="D68" s="8"/>
     </row>
-    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>102</v>
       </c>
@@ -7414,7 +7423,7 @@
       </c>
       <c r="D69" s="8"/>
     </row>
-    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>103</v>
       </c>
@@ -7426,7 +7435,7 @@
       </c>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>104</v>
       </c>
@@ -7438,7 +7447,7 @@
       </c>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>105</v>
       </c>
@@ -7450,7 +7459,7 @@
       </c>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>106</v>
       </c>
@@ -7462,7 +7471,7 @@
       </c>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>107</v>
       </c>
@@ -7476,7 +7485,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>108</v>
       </c>
@@ -7488,7 +7497,7 @@
       </c>
       <c r="D75" s="8"/>
     </row>
-    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>109</v>
       </c>
@@ -7500,7 +7509,7 @@
       </c>
       <c r="D76" s="8"/>
     </row>
-    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>110</v>
       </c>
@@ -7512,7 +7521,7 @@
       </c>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>111</v>
       </c>
@@ -7524,7 +7533,7 @@
       </c>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>112</v>
       </c>
@@ -7536,7 +7545,7 @@
       </c>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>126</v>
       </c>
@@ -7548,7 +7557,7 @@
       </c>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>127</v>
       </c>
@@ -7560,7 +7569,7 @@
       </c>
       <c r="D81" s="8"/>
     </row>
-    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>128</v>
       </c>
@@ -7572,7 +7581,7 @@
       </c>
       <c r="D82" s="8"/>
     </row>
-    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>130</v>
       </c>
@@ -7584,7 +7593,7 @@
       </c>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>131</v>
       </c>
@@ -7598,7 +7607,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>132</v>
       </c>
@@ -7612,7 +7621,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>133</v>
       </c>
@@ -7626,7 +7635,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>134</v>
       </c>
@@ -7638,7 +7647,7 @@
       </c>
       <c r="D87" s="8"/>
     </row>
-    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>135</v>
       </c>
@@ -7650,7 +7659,7 @@
       </c>
       <c r="D88" s="8"/>
     </row>
-    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>137</v>
       </c>
@@ -7662,7 +7671,7 @@
       </c>
       <c r="D89" s="8"/>
     </row>
-    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <v>138</v>
       </c>
@@ -7674,7 +7683,7 @@
       </c>
       <c r="D90" s="12"/>
     </row>
-    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>139</v>
       </c>
@@ -7686,7 +7695,7 @@
       </c>
       <c r="D91" s="8"/>
     </row>
-    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>140</v>
       </c>
@@ -7700,7 +7709,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>141</v>
       </c>
@@ -7714,7 +7723,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>142</v>
       </c>
@@ -7728,7 +7737,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>143</v>
       </c>
@@ -7742,7 +7751,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>144</v>
       </c>
@@ -7754,7 +7763,7 @@
       </c>
       <c r="D96" s="8"/>
     </row>
-    <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>145</v>
       </c>
@@ -7766,7 +7775,7 @@
       </c>
       <c r="D97" s="8"/>
     </row>
-    <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>146</v>
       </c>
@@ -7780,7 +7789,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>147</v>
       </c>
@@ -7794,7 +7803,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>148</v>
       </c>
@@ -7806,7 +7815,7 @@
       </c>
       <c r="D100" s="8"/>
     </row>
-    <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>149</v>
       </c>
@@ -7818,7 +7827,7 @@
       </c>
       <c r="D101" s="8"/>
     </row>
-    <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>150</v>
       </c>
@@ -7830,7 +7839,7 @@
       </c>
       <c r="D102" s="8"/>
     </row>
-    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>151</v>
       </c>
@@ -7842,7 +7851,7 @@
       </c>
       <c r="D103" s="8"/>
     </row>
-    <row r="104" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>152</v>
       </c>
@@ -7854,7 +7863,7 @@
       </c>
       <c r="D104" s="9"/>
     </row>
-    <row r="105" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>153</v>
       </c>
@@ -7866,7 +7875,7 @@
       </c>
       <c r="D105" s="9"/>
     </row>
-    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>157</v>
       </c>
@@ -7880,7 +7889,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>158</v>
       </c>
@@ -7892,7 +7901,7 @@
       </c>
       <c r="D107" s="8"/>
     </row>
-    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>159</v>
       </c>
@@ -7906,7 +7915,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>168</v>
       </c>
@@ -7918,7 +7927,7 @@
       </c>
       <c r="D109" s="9"/>
     </row>
-    <row r="110" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>184</v>
       </c>
@@ -7932,7 +7941,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>192</v>
       </c>
@@ -7946,7 +7955,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>219</v>
       </c>
@@ -7960,7 +7969,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>220</v>
       </c>
@@ -7972,7 +7981,7 @@
       </c>
       <c r="D113" s="8"/>
     </row>
-    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>221</v>
       </c>
@@ -7984,7 +7993,7 @@
       </c>
       <c r="D114" s="8"/>
     </row>
-    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>222</v>
       </c>
@@ -7996,7 +8005,7 @@
       </c>
       <c r="D115" s="8"/>
     </row>
-    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>223</v>
       </c>
@@ -8008,7 +8017,7 @@
       </c>
       <c r="D116" s="8"/>
     </row>
-    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>224</v>
       </c>
@@ -8020,7 +8029,7 @@
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>225</v>
       </c>
@@ -8032,7 +8041,7 @@
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>226</v>
       </c>
@@ -8046,7 +8055,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>227</v>
       </c>
@@ -8060,7 +8069,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>228</v>
       </c>
@@ -8074,7 +8083,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>229</v>
       </c>
@@ -8088,7 +8097,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A123" s="12">
         <v>236</v>
       </c>
@@ -8100,7 +8109,7 @@
       </c>
       <c r="D123" s="12"/>
     </row>
-    <row r="124" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A124" s="13">
         <v>238</v>
       </c>
@@ -8114,7 +8123,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>259</v>
       </c>
@@ -8126,7 +8135,7 @@
       </c>
       <c r="D125" s="12"/>
     </row>
-    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>274</v>
       </c>
@@ -8138,7 +8147,7 @@
       </c>
       <c r="D126" s="12"/>
     </row>
-    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A127" s="12">
         <v>276</v>
       </c>
@@ -8150,7 +8159,7 @@
       </c>
       <c r="D127" s="12"/>
     </row>
-    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A128" s="12">
         <v>280</v>
       </c>
@@ -8162,7 +8171,7 @@
       </c>
       <c r="D128" s="12"/>
     </row>
-    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A129" s="12">
         <v>281</v>
       </c>
@@ -8174,7 +8183,7 @@
       </c>
       <c r="D129" s="12"/>
     </row>
-    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A130" s="12">
         <v>282</v>
       </c>
@@ -8186,7 +8195,7 @@
       </c>
       <c r="D130" s="12"/>
     </row>
-    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A131" s="12">
         <v>283</v>
       </c>
@@ -8198,7 +8207,7 @@
       </c>
       <c r="D131" s="12"/>
     </row>
-    <row r="132" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A132" s="12">
         <v>288</v>
       </c>
@@ -8212,7 +8221,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A133" s="12">
         <v>297</v>
       </c>
@@ -8224,7 +8233,7 @@
       </c>
       <c r="D133" s="12"/>
     </row>
-    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A134" s="12">
         <v>312</v>
       </c>
@@ -8236,7 +8245,7 @@
       </c>
       <c r="D134" s="12"/>
     </row>
-    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A135" s="12">
         <v>314</v>
       </c>
@@ -8248,7 +8257,7 @@
       </c>
       <c r="D135" s="12"/>
     </row>
-    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A136" s="12">
         <v>318</v>
       </c>
@@ -8260,7 +8269,7 @@
       </c>
       <c r="D136" s="12"/>
     </row>
-    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>319</v>
       </c>
@@ -8272,7 +8281,7 @@
       </c>
       <c r="D137" s="12"/>
     </row>
-    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>320</v>
       </c>
@@ -8284,7 +8293,7 @@
       </c>
       <c r="D138" s="12"/>
     </row>
-    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>321</v>
       </c>
@@ -8296,7 +8305,7 @@
       </c>
       <c r="D139" s="12"/>
     </row>
-    <row r="140" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>326</v>
       </c>
@@ -8310,7 +8319,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>335</v>
       </c>
@@ -8322,7 +8331,7 @@
       </c>
       <c r="D141" s="12"/>
     </row>
-    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>350</v>
       </c>
@@ -8336,7 +8345,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>352</v>
       </c>
@@ -8348,7 +8357,7 @@
       </c>
       <c r="D143" s="12"/>
     </row>
-    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>356</v>
       </c>
@@ -8360,7 +8369,7 @@
       </c>
       <c r="D144" s="12"/>
     </row>
-    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>358</v>
       </c>
@@ -8372,7 +8381,7 @@
       </c>
       <c r="D145" s="12"/>
     </row>
-    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>359</v>
       </c>
@@ -8384,7 +8393,7 @@
       </c>
       <c r="D146" s="12"/>
     </row>
-    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>360</v>
       </c>
@@ -8396,7 +8405,7 @@
       </c>
       <c r="D147" s="12"/>
     </row>
-    <row r="148" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>365</v>
       </c>
@@ -8410,7 +8419,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>442</v>
       </c>
@@ -8422,7 +8431,7 @@
       </c>
       <c r="D149" s="12"/>
     </row>
-    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>454</v>
       </c>
@@ -8436,7 +8445,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A151" s="13">
         <v>466</v>
       </c>
@@ -8450,7 +8459,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>473</v>
       </c>
@@ -8464,7 +8473,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A153" s="14">
         <v>490</v>
       </c>
@@ -8478,7 +8487,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A154" s="14">
         <v>498</v>
       </c>
@@ -8492,7 +8501,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A155" s="16">
         <v>499</v>
       </c>
@@ -8506,7 +8515,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A156" s="16">
         <v>500</v>
       </c>
@@ -8518,7 +8527,7 @@
       </c>
       <c r="D156" s="19"/>
     </row>
-    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A157" s="16">
         <v>501</v>
       </c>
@@ -8530,7 +8539,7 @@
       </c>
       <c r="D157" s="19"/>
     </row>
-    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A158" s="16">
         <v>502</v>
       </c>
@@ -8542,7 +8551,7 @@
       </c>
       <c r="D158" s="19"/>
     </row>
-    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A159" s="16">
         <v>503</v>
       </c>
@@ -8554,7 +8563,7 @@
       </c>
       <c r="D159" s="19"/>
     </row>
-    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A160" s="16">
         <v>504</v>
       </c>
@@ -8566,7 +8575,7 @@
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="38" x14ac:dyDescent="0.25">
       <c r="A161" s="16">
         <v>505</v>
       </c>
@@ -8580,7 +8589,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A162" s="16">
         <v>506</v>
       </c>
@@ -8592,7 +8601,7 @@
       </c>
       <c r="D162" s="19"/>
     </row>
-    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A163" s="14">
         <v>640</v>
       </c>
@@ -8606,7 +8615,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A164" s="14">
         <v>641</v>
       </c>
@@ -8620,7 +8629,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A165" s="14">
         <v>642</v>
       </c>
@@ -8634,7 +8643,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A166" s="12">
         <v>648</v>
       </c>
@@ -8648,7 +8657,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A167" s="12">
         <v>649</v>
       </c>
@@ -8662,7 +8671,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A168" s="12">
         <v>652</v>
       </c>
@@ -8676,7 +8685,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A169" s="12">
         <v>653</v>
       </c>
@@ -8690,7 +8699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A170" s="12">
         <v>654</v>
       </c>
@@ -8704,7 +8713,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A171" s="12">
         <v>655</v>
       </c>
@@ -8718,7 +8727,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A172" s="12">
         <v>656</v>
       </c>
@@ -8732,7 +8741,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A173" s="12">
         <v>657</v>
       </c>
@@ -8746,7 +8755,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A174" s="12">
         <v>658</v>
       </c>
@@ -8760,7 +8769,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A175" s="12">
         <v>659</v>
       </c>
@@ -8774,7 +8783,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A176" s="12">
         <v>660</v>
       </c>
@@ -8788,7 +8797,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" ht="38" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>661</v>
       </c>
@@ -8802,7 +8811,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A178" s="13">
         <v>662</v>
       </c>
@@ -8814,7 +8823,7 @@
       </c>
       <c r="D178" s="13"/>
     </row>
-    <row r="179" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A179" s="12">
         <v>664</v>
       </c>
@@ -8828,7 +8837,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A180" s="12">
         <v>666</v>
       </c>
@@ -8842,7 +8851,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A181" s="12">
         <v>667</v>
       </c>
@@ -8856,7 +8865,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A182" s="12">
         <v>668</v>
       </c>
@@ -8870,7 +8879,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A183" s="12">
         <v>672</v>
       </c>
@@ -8884,7 +8893,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A184" s="12">
         <v>687</v>
       </c>
@@ -8898,7 +8907,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A185" s="12">
         <v>689</v>
       </c>
@@ -8912,7 +8921,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A186" s="12">
         <v>690</v>
       </c>
@@ -8924,7 +8933,7 @@
       </c>
       <c r="D186" s="12"/>
     </row>
-    <row r="187" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A187" s="12">
         <v>691</v>
       </c>
@@ -8938,7 +8947,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A188" s="12">
         <v>692</v>
       </c>
@@ -8952,7 +8961,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A189" s="12">
         <v>693</v>
       </c>
@@ -8964,7 +8973,7 @@
       </c>
       <c r="D189" s="12"/>
     </row>
-    <row r="190" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A190" s="12">
         <v>694</v>
       </c>
@@ -8978,7 +8987,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>695</v>
       </c>
@@ -8990,7 +8999,7 @@
       </c>
       <c r="D191" s="12"/>
     </row>
-    <row r="192" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>696</v>
       </c>
@@ -9004,7 +9013,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>716</v>
       </c>
@@ -9016,7 +9025,7 @@
       </c>
       <c r="D193" s="12"/>
     </row>
-    <row r="194" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>717</v>
       </c>
@@ -9028,7 +9037,7 @@
       </c>
       <c r="D194" s="12"/>
     </row>
-    <row r="195" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>718</v>
       </c>
@@ -9042,7 +9051,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>723</v>
       </c>
@@ -9056,7 +9065,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>724</v>
       </c>
@@ -9068,7 +9077,7 @@
       </c>
       <c r="D197" s="12"/>
     </row>
-    <row r="198" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>750</v>
       </c>
@@ -9082,7 +9091,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>751</v>
       </c>
@@ -9096,7 +9105,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A200" s="13">
         <v>755</v>
       </c>
@@ -9110,7 +9119,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>758</v>
       </c>
@@ -9122,7 +9131,7 @@
       </c>
       <c r="D201" s="12"/>
     </row>
-    <row r="202" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A202" s="13">
         <v>766</v>
       </c>
@@ -9136,7 +9145,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A203" s="13">
         <v>767</v>
       </c>
@@ -9150,7 +9159,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" ht="38" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>777</v>
       </c>
@@ -9164,7 +9173,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>778</v>
       </c>
@@ -9178,7 +9187,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A206" s="13">
         <v>783</v>
       </c>
@@ -9192,7 +9201,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A207" s="13">
         <v>784</v>
       </c>
@@ -9206,7 +9215,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A208" s="13">
         <v>785</v>
       </c>
@@ -9220,7 +9229,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>790</v>
       </c>
@@ -9232,7 +9241,7 @@
       </c>
       <c r="D209" s="12"/>
     </row>
-    <row r="210" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>791</v>
       </c>
@@ -9244,7 +9253,7 @@
       </c>
       <c r="D210" s="12"/>
     </row>
-    <row r="211" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>792</v>
       </c>
@@ -9256,7 +9265,7 @@
       </c>
       <c r="D211" s="12"/>
     </row>
-    <row r="212" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>793</v>
       </c>
@@ -9268,7 +9277,7 @@
       </c>
       <c r="D212" s="12"/>
     </row>
-    <row r="213" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>794</v>
       </c>
@@ -9280,7 +9289,7 @@
       </c>
       <c r="D213" s="12"/>
     </row>
-    <row r="214" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>795</v>
       </c>
@@ -9292,7 +9301,7 @@
       </c>
       <c r="D214" s="12"/>
     </row>
-    <row r="215" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>796</v>
       </c>
@@ -9306,7 +9315,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A216" s="13">
         <v>799</v>
       </c>
@@ -9318,7 +9327,7 @@
       </c>
       <c r="D216" s="13"/>
     </row>
-    <row r="217" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A217" s="13">
         <v>800</v>
       </c>
@@ -9330,7 +9339,7 @@
       </c>
       <c r="D217" s="13"/>
     </row>
-    <row r="218" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A218" s="12">
         <v>801</v>
       </c>
@@ -9342,7 +9351,7 @@
       </c>
       <c r="D218" s="12"/>
     </row>
-    <row r="219" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A219" s="12">
         <v>802</v>
       </c>
@@ -9354,7 +9363,7 @@
       </c>
       <c r="D219" s="12"/>
     </row>
-    <row r="220" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A220" s="12">
         <v>803</v>
       </c>
@@ -9366,7 +9375,7 @@
       </c>
       <c r="D220" s="12"/>
     </row>
-    <row r="221" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A221" s="13">
         <v>804</v>
       </c>
@@ -9380,7 +9389,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A222" s="12">
         <v>806</v>
       </c>
@@ -9394,7 +9403,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" ht="26" x14ac:dyDescent="0.25">
       <c r="A223" s="13">
         <v>1016</v>
       </c>
@@ -9408,7 +9417,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A224" s="12">
         <v>1028</v>
       </c>
@@ -9422,7 +9431,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A225" s="23">
         <v>1032</v>
       </c>
@@ -9434,7 +9443,7 @@
       </c>
       <c r="D225" s="21"/>
     </row>
-    <row r="226" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A226" s="23">
         <v>1033</v>
       </c>
@@ -9446,7 +9455,7 @@
       </c>
       <c r="D226" s="21"/>
     </row>
-    <row r="227" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A227" s="12">
         <v>1034</v>
       </c>
@@ -9460,7 +9469,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>1035</v>
       </c>
@@ -9474,7 +9483,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A229" s="23">
         <v>1036</v>
       </c>
@@ -9486,7 +9495,7 @@
       </c>
       <c r="D229" s="12"/>
     </row>
-    <row r="230" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A230" s="23">
         <v>1038</v>
       </c>
@@ -9498,7 +9507,7 @@
       </c>
       <c r="D230" s="12"/>
     </row>
-    <row r="231" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A231" s="23">
         <v>1039</v>
       </c>
@@ -9510,7 +9519,7 @@
       </c>
       <c r="D231" s="12"/>
     </row>
-    <row r="232" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A232" s="12">
         <v>1040</v>
       </c>
@@ -9522,7 +9531,7 @@
       </c>
       <c r="D232" s="12"/>
     </row>
-    <row r="233" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A233" s="12">
         <v>1041</v>
       </c>
@@ -9534,7 +9543,7 @@
       </c>
       <c r="D233" s="12"/>
     </row>
-    <row r="234" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A234" s="23">
         <v>1042</v>
       </c>
@@ -9546,7 +9555,7 @@
       </c>
       <c r="D234" s="12"/>
     </row>
-    <row r="235" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A235" s="12">
         <v>1049</v>
       </c>
@@ -9558,7 +9567,7 @@
       </c>
       <c r="D235" s="12"/>
     </row>
-    <row r="236" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A236" s="23">
         <v>1061</v>
       </c>
@@ -9570,7 +9579,7 @@
       </c>
       <c r="D236" s="25"/>
     </row>
-    <row r="237" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A237" s="23">
         <v>1062</v>
       </c>
@@ -9582,7 +9591,7 @@
       </c>
       <c r="D237" s="25"/>
     </row>
-    <row r="238" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A238" s="12">
         <v>1063</v>
       </c>
@@ -9594,7 +9603,7 @@
       </c>
       <c r="D238" s="25"/>
     </row>
-    <row r="239" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A239" s="12">
         <v>1064</v>
       </c>
@@ -9606,7 +9615,7 @@
       </c>
       <c r="D239" s="25"/>
     </row>
-    <row r="240" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A240" s="23">
         <v>1065</v>
       </c>
@@ -9620,7 +9629,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A241" s="23">
         <v>1067</v>
       </c>
@@ -9632,7 +9641,7 @@
       </c>
       <c r="D241" s="26"/>
     </row>
-    <row r="242" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A242" s="23">
         <v>1068</v>
       </c>
@@ -9644,7 +9653,7 @@
       </c>
       <c r="D242" s="26"/>
     </row>
-    <row r="243" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A243" s="12">
         <v>1069</v>
       </c>
@@ -9656,7 +9665,7 @@
       </c>
       <c r="D243" s="26"/>
     </row>
-    <row r="244" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A244" s="12">
         <v>1070</v>
       </c>
@@ -9668,7 +9677,7 @@
       </c>
       <c r="D244" s="26"/>
     </row>
-    <row r="245" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A245" s="23">
         <v>1071</v>
       </c>
@@ -9680,7 +9689,7 @@
       </c>
       <c r="D245" s="26"/>
     </row>
-    <row r="246" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A246" s="23">
         <v>1078</v>
       </c>
@@ -9694,7 +9703,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A247" s="23">
         <v>1079</v>
       </c>
@@ -9706,7 +9715,7 @@
       </c>
       <c r="D247" s="25"/>
     </row>
-    <row r="248" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A248" s="12">
         <v>1080</v>
       </c>
@@ -9720,7 +9729,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A249" s="12">
         <v>1081</v>
       </c>
@@ -9732,7 +9741,7 @@
       </c>
       <c r="D249" s="26"/>
     </row>
-    <row r="250" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A250" s="23">
         <v>1082</v>
       </c>
@@ -9746,7 +9755,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A251" s="23">
         <v>1083</v>
       </c>
@@ -9758,7 +9767,7 @@
       </c>
       <c r="D251" s="25"/>
     </row>
-    <row r="252" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A252" s="12">
         <v>1084</v>
       </c>
@@ -9770,7 +9779,7 @@
       </c>
       <c r="D252" s="25"/>
     </row>
-    <row r="253" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A253" s="12">
         <v>1085</v>
       </c>
@@ -9782,7 +9791,7 @@
       </c>
       <c r="D253" s="25"/>
     </row>
-    <row r="254" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A254" s="23">
         <v>1090</v>
       </c>
@@ -9794,7 +9803,7 @@
       </c>
       <c r="D254" s="25"/>
     </row>
-    <row r="255" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A255" s="23">
         <v>1091</v>
       </c>
@@ -9806,7 +9815,7 @@
       </c>
       <c r="D255" s="25"/>
     </row>
-    <row r="256" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A256" s="23">
         <v>1092</v>
       </c>
@@ -9818,7 +9827,7 @@
       </c>
       <c r="D256" s="25"/>
     </row>
-    <row r="257" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A257" s="23">
         <v>1093</v>
       </c>
@@ -9841,17 +9850,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E212"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E213"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" customWidth="1"/>
+    <col min="3" max="3" width="54.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.453125" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>322</v>
       </c>
@@ -9868,7 +9877,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>327</v>
       </c>
@@ -9881,7 +9890,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>329</v>
       </c>
@@ -9896,7 +9905,7 @@
       </c>
       <c r="E3" s="29"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>332</v>
       </c>
@@ -9911,7 +9920,7 @@
       </c>
       <c r="E4" s="29"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>335</v>
       </c>
@@ -9926,7 +9935,7 @@
       </c>
       <c r="E5" s="29"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>338</v>
       </c>
@@ -9941,7 +9950,7 @@
       </c>
       <c r="E6" s="29"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>341</v>
       </c>
@@ -9956,7 +9965,7 @@
       </c>
       <c r="E7" s="29"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>345</v>
       </c>
@@ -9971,7 +9980,7 @@
       </c>
       <c r="E8" s="29"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>347</v>
       </c>
@@ -9986,7 +9995,7 @@
       </c>
       <c r="E9" s="29"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>349</v>
       </c>
@@ -10001,7 +10010,7 @@
       </c>
       <c r="E10" s="29"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>351</v>
       </c>
@@ -10016,7 +10025,7 @@
       </c>
       <c r="E11" s="29"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>353</v>
       </c>
@@ -10031,7 +10040,7 @@
       </c>
       <c r="E12" s="29"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>354</v>
       </c>
@@ -10046,7 +10055,7 @@
       </c>
       <c r="E13" s="29"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>357</v>
       </c>
@@ -10061,7 +10070,7 @@
       </c>
       <c r="E14" s="29"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>360</v>
       </c>
@@ -10076,7 +10085,7 @@
       </c>
       <c r="E15" s="31"/>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>363</v>
       </c>
@@ -10091,7 +10100,7 @@
       </c>
       <c r="E16" s="31"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>366</v>
       </c>
@@ -10104,7 +10113,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="31"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>368</v>
       </c>
@@ -10117,7 +10126,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="31"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
         <v>370</v>
       </c>
@@ -10132,7 +10141,7 @@
       </c>
       <c r="E19" s="31"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>373</v>
       </c>
@@ -10145,7 +10154,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="31"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>375</v>
       </c>
@@ -10158,7 +10167,7 @@
       <c r="D21" s="14"/>
       <c r="E21" s="31"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>377</v>
       </c>
@@ -10173,7 +10182,7 @@
       </c>
       <c r="E22" s="31"/>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>380</v>
       </c>
@@ -10188,7 +10197,7 @@
       </c>
       <c r="E23" s="35"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
         <v>382</v>
       </c>
@@ -10203,7 +10212,7 @@
       </c>
       <c r="E24" s="31"/>
     </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>386</v>
       </c>
@@ -10218,7 +10227,7 @@
       </c>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>389</v>
       </c>
@@ -10233,7 +10242,7 @@
       </c>
       <c r="E26" s="29"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>392</v>
       </c>
@@ -10248,7 +10257,7 @@
       </c>
       <c r="E27" s="29"/>
     </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>395</v>
       </c>
@@ -10263,7 +10272,7 @@
       </c>
       <c r="E28" s="29"/>
     </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>398</v>
       </c>
@@ -10276,7 +10285,7 @@
       <c r="D29" s="6"/>
       <c r="E29" s="29"/>
     </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>400</v>
       </c>
@@ -10289,7 +10298,7 @@
       <c r="D30" s="6"/>
       <c r="E30" s="29"/>
     </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>402</v>
       </c>
@@ -10302,7 +10311,7 @@
       <c r="D31" s="6"/>
       <c r="E31" s="29"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
         <v>404</v>
       </c>
@@ -10315,7 +10324,7 @@
       <c r="D32" s="6"/>
       <c r="E32" s="29"/>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
         <v>406</v>
       </c>
@@ -10328,7 +10337,7 @@
       <c r="D33" s="6"/>
       <c r="E33" s="29"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
         <v>408</v>
       </c>
@@ -10343,7 +10352,7 @@
       </c>
       <c r="E34" s="29"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
         <v>412</v>
       </c>
@@ -10358,7 +10367,7 @@
       </c>
       <c r="E35" s="29"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>415</v>
       </c>
@@ -10375,7 +10384,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>420</v>
       </c>
@@ -10388,7 +10397,7 @@
       <c r="D37" s="6"/>
       <c r="E37" s="29"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>422</v>
       </c>
@@ -10401,7 +10410,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
         <v>424</v>
       </c>
@@ -10418,7 +10427,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
         <v>428</v>
       </c>
@@ -10431,7 +10440,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="29"/>
     </row>
-    <row r="41" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
         <v>430</v>
       </c>
@@ -10444,7 +10453,7 @@
       <c r="D41" s="6"/>
       <c r="E41" s="29"/>
     </row>
-    <row r="42" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
         <v>432</v>
       </c>
@@ -10461,7 +10470,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A43" s="28" t="s">
         <v>434</v>
       </c>
@@ -10474,7 +10483,7 @@
       <c r="D43" s="6"/>
       <c r="E43" s="29"/>
     </row>
-    <row r="44" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
         <v>436</v>
       </c>
@@ -10487,7 +10496,7 @@
       <c r="D44" s="6"/>
       <c r="E44" s="29"/>
     </row>
-    <row r="45" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="38.5" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
         <v>438</v>
       </c>
@@ -10504,7 +10513,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
         <v>441</v>
       </c>
@@ -10517,7 +10526,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="29"/>
     </row>
-    <row r="47" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A47" s="28" t="s">
         <v>443</v>
       </c>
@@ -10530,7 +10539,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="29"/>
     </row>
-    <row r="48" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
         <v>445</v>
       </c>
@@ -10547,7 +10556,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
         <v>449</v>
       </c>
@@ -10562,7 +10571,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
         <v>452</v>
       </c>
@@ -10577,7 +10586,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
         <v>454</v>
       </c>
@@ -10594,7 +10603,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
         <v>457</v>
       </c>
@@ -10611,7 +10620,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A53" s="28" t="s">
         <v>460</v>
       </c>
@@ -10628,7 +10637,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
         <v>462</v>
       </c>
@@ -10641,7 +10650,7 @@
       <c r="D54" s="6"/>
       <c r="E54" s="29"/>
     </row>
-    <row r="55" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
         <v>464</v>
       </c>
@@ -10654,7 +10663,7 @@
       <c r="D55" s="6"/>
       <c r="E55" s="29"/>
     </row>
-    <row r="56" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
         <v>466</v>
       </c>
@@ -10671,7 +10680,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
         <v>469</v>
       </c>
@@ -10684,7 +10693,7 @@
       <c r="D57" s="6"/>
       <c r="E57" s="29"/>
     </row>
-    <row r="58" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
         <v>471</v>
       </c>
@@ -10697,7 +10706,7 @@
       <c r="D58" s="6"/>
       <c r="E58" s="29"/>
     </row>
-    <row r="59" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A59" s="28" t="s">
         <v>473</v>
       </c>
@@ -10712,7 +10721,7 @@
       </c>
       <c r="E59" s="8"/>
     </row>
-    <row r="60" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
         <v>475</v>
       </c>
@@ -10725,7 +10734,7 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row r="61" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
         <v>477</v>
       </c>
@@ -10740,7 +10749,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
         <v>479</v>
       </c>
@@ -10757,7 +10766,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
         <v>481</v>
       </c>
@@ -10774,7 +10783,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
         <v>483</v>
       </c>
@@ -10791,7 +10800,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
         <v>487</v>
       </c>
@@ -10806,7 +10815,7 @@
       </c>
       <c r="E65" s="29"/>
     </row>
-    <row r="66" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>490</v>
       </c>
@@ -10821,7 +10830,7 @@
       </c>
       <c r="E66" s="29"/>
     </row>
-    <row r="67" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
         <v>492</v>
       </c>
@@ -10836,7 +10845,7 @@
       </c>
       <c r="E67" s="29"/>
     </row>
-    <row r="68" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
         <v>494</v>
       </c>
@@ -10851,7 +10860,7 @@
       </c>
       <c r="E68" s="29"/>
     </row>
-    <row r="69" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A69" s="28" t="s">
         <v>496</v>
       </c>
@@ -10866,7 +10875,7 @@
       </c>
       <c r="E69" s="29"/>
     </row>
-    <row r="70" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
         <v>498</v>
       </c>
@@ -10881,7 +10890,7 @@
       </c>
       <c r="E70" s="36"/>
     </row>
-    <row r="71" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
         <v>502</v>
       </c>
@@ -10896,7 +10905,7 @@
       </c>
       <c r="E71" s="29"/>
     </row>
-    <row r="72" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
         <v>506</v>
       </c>
@@ -10911,7 +10920,7 @@
       </c>
       <c r="E72" s="29"/>
     </row>
-    <row r="73" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
         <v>510</v>
       </c>
@@ -10926,7 +10935,7 @@
       </c>
       <c r="E73" s="29"/>
     </row>
-    <row r="74" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
         <v>513</v>
       </c>
@@ -10941,7 +10950,7 @@
       </c>
       <c r="E74" s="36"/>
     </row>
-    <row r="75" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
         <v>517</v>
       </c>
@@ -10958,312 +10967,312 @@
         <v>520</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="30" t="s">
+    <row r="76" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A76" s="28" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E76" s="29"/>
+    </row>
+    <row r="77" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A77" s="30" t="s">
         <v>521</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B77" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C77" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D77" s="14" t="s">
         <v>523</v>
       </c>
-      <c r="E76" s="31"/>
-    </row>
-    <row r="77" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="30" t="s">
+      <c r="E77" s="31"/>
+    </row>
+    <row r="78" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A78" s="30" t="s">
         <v>524</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B78" s="16">
         <v>0</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C78" s="17" t="s">
         <v>525</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D78" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="E77" s="31"/>
-    </row>
-    <row r="78" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="30" t="s">
+      <c r="E78" s="31"/>
+    </row>
+    <row r="79" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A79" s="30" t="s">
         <v>527</v>
-      </c>
-      <c r="B78" s="16">
-        <v>1</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E78" s="31"/>
-    </row>
-    <row r="79" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="30" t="s">
-        <v>530</v>
       </c>
       <c r="B79" s="16">
         <v>1</v>
       </c>
       <c r="C79" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="E79" s="31"/>
+    </row>
+    <row r="80" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A80" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="B80" s="16">
+        <v>1</v>
+      </c>
+      <c r="C80" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D80" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="E79" s="31"/>
-    </row>
-    <row r="80" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="30" t="s">
+      <c r="E80" s="31"/>
+    </row>
+    <row r="81" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A81" s="30" t="s">
         <v>533</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B81" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C81" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D81" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="E80" s="31"/>
-    </row>
-    <row r="81" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="30" t="s">
+      <c r="E81" s="31"/>
+    </row>
+    <row r="82" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A82" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="C81" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="E81" s="31"/>
-    </row>
-    <row r="82" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="28" t="s">
-        <v>540</v>
       </c>
       <c r="B82" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="E82" s="31"/>
+    </row>
+    <row r="83" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A83" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="29"/>
-    </row>
-    <row r="83" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="28" t="s">
+      <c r="D83" s="6"/>
+      <c r="E83" s="29"/>
+    </row>
+    <row r="84" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A84" s="28" t="s">
         <v>542</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B84" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C84" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D84" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="E83" s="29"/>
-    </row>
-    <row r="84" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="28" t="s">
+      <c r="E84" s="29"/>
+    </row>
+    <row r="85" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A85" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="B84" s="6">
+      <c r="B85" s="6">
         <v>1</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C85" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="D84" s="14" t="s">
+      <c r="D85" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="E84" s="29"/>
-    </row>
-    <row r="85" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="28" t="s">
+      <c r="E85" s="29"/>
+    </row>
+    <row r="86" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A86" s="28" t="s">
         <v>548</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B86" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C86" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D86" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E85" s="29"/>
-    </row>
-    <row r="86" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="28" t="s">
+      <c r="E86" s="29"/>
+    </row>
+    <row r="87" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A87" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B87" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C87" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D87" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E86" s="29"/>
-    </row>
-    <row r="87" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A87" s="28" t="s">
+      <c r="E87" s="29"/>
+    </row>
+    <row r="88" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="28" t="s">
         <v>554</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B88" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C88" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D88" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="E87" s="29"/>
-    </row>
-    <row r="88" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="28" t="s">
+      <c r="E88" s="29"/>
+    </row>
+    <row r="89" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A89" s="28" t="s">
         <v>557</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B89" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C89" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D89" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="E88" s="8"/>
-    </row>
-    <row r="89" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="28" t="s">
+      <c r="E89" s="8"/>
+    </row>
+    <row r="90" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A90" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B90" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C90" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D90" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E90" s="8" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A90" s="28" t="s">
+    <row r="91" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A91" s="28" t="s">
         <v>565</v>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="E90" s="8"/>
-    </row>
-    <row r="91" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="28" t="s">
-        <v>568</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E91" s="8"/>
     </row>
-    <row r="92" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B92" s="8"/>
       <c r="C92" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E92" s="8"/>
     </row>
-    <row r="93" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A93" s="28" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B93" s="8"/>
       <c r="C93" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B94" s="8"/>
       <c r="C94" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E94" s="8"/>
     </row>
-    <row r="95" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A95" s="28" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="E95" s="8"/>
+    </row>
+    <row r="96" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A96" s="28" t="s">
+        <v>580</v>
+      </c>
+      <c r="B96" s="8"/>
+      <c r="C96" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D96" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="E95" s="8"/>
-    </row>
-    <row r="96" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="28" t="s">
+      <c r="E96" s="8"/>
+    </row>
+    <row r="97" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A97" s="28" t="s">
         <v>583</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="E96" s="8"/>
-    </row>
-    <row r="97" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="28" t="s">
-        <v>587</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>584</v>
@@ -11272,1597 +11281,1597 @@
         <v>585</v>
       </c>
       <c r="D97" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="E97" s="8"/>
+    </row>
+    <row r="98" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A98" s="28" t="s">
+        <v>587</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="D98" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="E97" s="8"/>
-    </row>
-    <row r="98" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A98" s="28" t="s">
+      <c r="E98" s="8"/>
+    </row>
+    <row r="99" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A99" s="28" t="s">
         <v>589</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B99" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C99" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D99" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E99" s="8" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="28" t="s">
+    <row r="100" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A100" s="28" t="s">
         <v>594</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B100" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C100" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D100" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E100" s="8" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="28" t="s">
+    <row r="101" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A101" s="28" t="s">
         <v>597</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B101" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C101" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D101" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="E100" s="8"/>
-    </row>
-    <row r="101" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="28" t="s">
+      <c r="E101" s="8"/>
+    </row>
+    <row r="102" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A102" s="28" t="s">
         <v>600</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="E101" s="8"/>
-    </row>
-    <row r="102" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="28" t="s">
-        <v>603</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="D102" s="8"/>
+        <v>601</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>602</v>
+      </c>
       <c r="E102" s="8"/>
     </row>
-    <row r="103" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A103" s="28" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C103" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+    </row>
+    <row r="104" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="28" t="s">
+        <v>605</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D104" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="E103" s="8"/>
-    </row>
-    <row r="104" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A104" s="28" t="s">
+      <c r="E104" s="8"/>
+    </row>
+    <row r="105" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A105" s="28" t="s">
         <v>608</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B105" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C105" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D105" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="E104" s="31"/>
-    </row>
-    <row r="105" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A105" s="78" t="s">
+      <c r="E105" s="31"/>
+    </row>
+    <row r="106" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A106" s="78" t="s">
         <v>1274</v>
       </c>
-      <c r="B105" s="79" t="s">
+      <c r="B106" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="C105" s="80" t="s">
+      <c r="C106" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="D105" s="79" t="s">
+      <c r="D106" s="79" t="s">
         <v>1275</v>
       </c>
-      <c r="E105" s="31"/>
-    </row>
-    <row r="106" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A106" s="28" t="s">
+      <c r="E106" s="31"/>
+    </row>
+    <row r="107" spans="1:5" ht="50.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="28" t="s">
         <v>611</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="E106" s="31"/>
-    </row>
-    <row r="107" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A107" s="28" t="s">
-        <v>614</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>409</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="E107" s="31"/>
+    </row>
+    <row r="108" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A108" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D108" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="E107" s="31"/>
-    </row>
-    <row r="108" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A108" s="28" t="s">
+      <c r="E108" s="31"/>
+    </row>
+    <row r="109" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A109" s="28" t="s">
         <v>617</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B109" s="6">
         <v>1</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C109" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D109" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="E108" s="31"/>
-    </row>
-    <row r="109" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A109" s="28" t="s">
+      <c r="E109" s="31"/>
+    </row>
+    <row r="110" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A110" s="28" t="s">
         <v>620</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B110" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C110" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D110" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="E109" s="31"/>
-    </row>
-    <row r="110" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A110" s="28" t="s">
+      <c r="E110" s="31"/>
+    </row>
+    <row r="111" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A111" s="28" t="s">
         <v>624</v>
-      </c>
-      <c r="B110" s="6">
-        <v>0</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="E110" s="31"/>
-    </row>
-    <row r="111" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A111" s="28" t="s">
-        <v>627</v>
       </c>
       <c r="B111" s="6">
         <v>0</v>
       </c>
       <c r="C111" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E111" s="31"/>
+    </row>
+    <row r="112" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A112" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="B112" s="6">
+        <v>0</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D112" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="E111" s="31"/>
-    </row>
-    <row r="112" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A112" s="28" t="s">
+      <c r="E112" s="31"/>
+    </row>
+    <row r="113" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A113" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B113" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C113" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D113" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="E112" s="31"/>
-    </row>
-    <row r="113" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A113" s="28" t="s">
+      <c r="E113" s="31"/>
+    </row>
+    <row r="114" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A114" s="28" t="s">
         <v>633</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B114" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C114" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D114" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="E113" s="31"/>
-    </row>
-    <row r="114" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A114" s="28" t="s">
+      <c r="E114" s="31"/>
+    </row>
+    <row r="115" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A115" s="28" t="s">
         <v>636</v>
-      </c>
-      <c r="B114" s="6">
-        <v>0</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="E114" s="31"/>
-    </row>
-    <row r="115" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A115" s="28" t="s">
-        <v>639</v>
       </c>
       <c r="B115" s="6">
         <v>0</v>
       </c>
       <c r="C115" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="E115" s="31"/>
+    </row>
+    <row r="116" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A116" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="B116" s="6">
+        <v>0</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D116" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="E115" s="31"/>
-    </row>
-    <row r="116" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="28" t="s">
+      <c r="E116" s="31"/>
+    </row>
+    <row r="117" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="28" t="s">
         <v>642</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="E116" s="31"/>
-    </row>
-    <row r="117" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A117" s="28" t="s">
-        <v>645</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E117" s="31"/>
     </row>
-    <row r="118" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E118" s="31"/>
     </row>
-    <row r="119" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A119" s="28" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E119" s="31"/>
     </row>
-    <row r="120" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>653</v>
       </c>
       <c r="E120" s="31"/>
     </row>
-    <row r="121" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A121" s="28" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E121" s="31"/>
     </row>
-    <row r="122" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" ht="50" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E122" s="31"/>
     </row>
-    <row r="123" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" ht="50" x14ac:dyDescent="0.25">
       <c r="A123" s="28" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>507</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="E123" s="31"/>
+    </row>
+    <row r="124" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A124" s="28" t="s">
+        <v>662</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C124" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D124" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="E123" s="31"/>
-    </row>
-    <row r="124" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A124" s="28" t="s">
+      <c r="E124" s="31"/>
+    </row>
+    <row r="125" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A125" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B125" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="C125" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D125" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="E124" s="37"/>
-    </row>
-    <row r="125" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A125" s="30" t="s">
+      <c r="E125" s="37"/>
+    </row>
+    <row r="126" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A126" s="30" t="s">
         <v>669</v>
       </c>
-      <c r="B125" s="32" t="s">
+      <c r="B126" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="C125" s="33" t="s">
+      <c r="C126" s="33" t="s">
         <v>670</v>
       </c>
-      <c r="D125" s="32"/>
-      <c r="E125" s="38"/>
-    </row>
-    <row r="126" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A126" s="30" t="s">
+      <c r="D126" s="32"/>
+      <c r="E126" s="38"/>
+    </row>
+    <row r="127" spans="1:5" ht="38" x14ac:dyDescent="0.25">
+      <c r="A127" s="30" t="s">
         <v>671</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>672</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>673</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>674</v>
-      </c>
-      <c r="E126" s="37"/>
-    </row>
-    <row r="127" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A127" s="30" t="s">
-        <v>675</v>
       </c>
       <c r="B127" s="16" t="s">
         <v>672</v>
       </c>
-      <c r="C127" s="17" t="s">
-        <v>676</v>
+      <c r="C127" s="7" t="s">
+        <v>673</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E127" s="37"/>
     </row>
-    <row r="128" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A128" s="30" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B128" s="16" t="s">
         <v>672</v>
       </c>
       <c r="C128" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="E128" s="37"/>
+    </row>
+    <row r="129" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A129" s="30" t="s">
+        <v>678</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="C129" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D129" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="E128" s="31"/>
-    </row>
-    <row r="129" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A129" s="28" t="s">
+      <c r="E129" s="31"/>
+    </row>
+    <row r="130" spans="1:5" ht="38" x14ac:dyDescent="0.25">
+      <c r="A130" s="28" t="s">
         <v>681</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B130" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C130" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D130" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="E129" s="31"/>
-    </row>
-    <row r="130" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A130" s="28" t="s">
+      <c r="E130" s="31"/>
+    </row>
+    <row r="131" spans="1:5" ht="75.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="28" t="s">
         <v>684</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="E130" s="31"/>
-    </row>
-    <row r="131" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A131" s="28" t="s">
-        <v>688</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>685</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>1278</v>
+        <v>687</v>
       </c>
       <c r="E131" s="31"/>
     </row>
-    <row r="132" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" ht="38" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>1276</v>
+        <v>688</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>685</v>
       </c>
       <c r="C132" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E132" s="31"/>
+    </row>
+    <row r="133" spans="1:5" ht="50.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="28" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>1277</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D133" s="6" t="s">
         <v>1279</v>
       </c>
-      <c r="E132" s="31"/>
-    </row>
-    <row r="133" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A133" s="28" t="s">
+      <c r="E133" s="31"/>
+    </row>
+    <row r="134" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="28" t="s">
         <v>690</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B134" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C134" s="7" t="s">
         <v>692</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="D134" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="E133" s="31"/>
-    </row>
-    <row r="134" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A134" s="28" t="s">
+      <c r="E134" s="31"/>
+    </row>
+    <row r="135" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A135" s="28" t="s">
         <v>694</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B135" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C135" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D135" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="E134" s="31"/>
-    </row>
-    <row r="135" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A135" s="28" t="s">
+      <c r="E135" s="31"/>
+    </row>
+    <row r="136" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A136" s="28" t="s">
         <v>697</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B136" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C136" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D136" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="E135" s="31"/>
-    </row>
-    <row r="136" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A136" s="28" t="s">
+      <c r="E136" s="31"/>
+    </row>
+    <row r="137" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="28" t="s">
         <v>700</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B137" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C137" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D137" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="E136" s="31"/>
-    </row>
-    <row r="137" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A137" s="28" t="s">
+      <c r="E137" s="31"/>
+    </row>
+    <row r="138" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A138" s="28" t="s">
         <v>704</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B138" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C138" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D138" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="E137" s="37"/>
-    </row>
-    <row r="138" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A138" s="28" t="s">
+      <c r="E138" s="37"/>
+    </row>
+    <row r="139" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A139" s="28" t="s">
         <v>707</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>708</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>709</v>
-      </c>
-      <c r="E138" s="31"/>
-    </row>
-    <row r="139" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A139" s="28" t="s">
-        <v>710</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>409</v>
       </c>
       <c r="C139" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="E139" s="31"/>
+    </row>
+    <row r="140" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A140" s="28" t="s">
+        <v>710</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D140" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="E139" s="31"/>
-    </row>
-    <row r="140" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A140" s="28" t="s">
+      <c r="E140" s="31"/>
+    </row>
+    <row r="141" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A141" s="28" t="s">
         <v>713</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B141" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C141" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D141" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="E140" s="31" t="s">
+      <c r="E141" s="31" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A141" s="78" t="s">
+    <row r="142" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A142" s="78" t="s">
         <v>1280</v>
       </c>
-      <c r="B141" s="79" t="s">
+      <c r="B142" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="C141" s="80" t="s">
+      <c r="C142" s="80" t="s">
         <v>1281</v>
       </c>
-      <c r="D141" s="79" t="s">
+      <c r="D142" s="79" t="s">
         <v>1282</v>
       </c>
-      <c r="E141" s="31"/>
-    </row>
-    <row r="142" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A142" s="28" t="s">
+      <c r="E142" s="31"/>
+    </row>
+    <row r="143" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A143" s="28" t="s">
         <v>717</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>719</v>
-      </c>
-      <c r="E142" s="31"/>
-    </row>
-    <row r="143" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A143" s="28" t="s">
-        <v>720</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E143" s="31"/>
     </row>
-    <row r="144" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E144" s="31"/>
     </row>
-    <row r="145" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A145" s="28" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C145" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="E145" s="31"/>
+    </row>
+    <row r="146" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A146" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C146" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D146" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="E145" s="31"/>
-    </row>
-    <row r="146" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A146" s="28" t="s">
+      <c r="E146" s="31"/>
+    </row>
+    <row r="147" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A147" s="28" t="s">
         <v>729</v>
       </c>
-      <c r="B146" s="14">
+      <c r="B147" s="14">
         <v>1</v>
       </c>
-      <c r="C146" s="15" t="s">
+      <c r="C147" s="15" t="s">
         <v>730</v>
       </c>
-      <c r="D146" s="14" t="s">
+      <c r="D147" s="14" t="s">
         <v>731</v>
       </c>
-      <c r="E146" s="31" t="s">
+      <c r="E147" s="31" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A147" s="28" t="s">
+    <row r="148" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A148" s="28" t="s">
         <v>733</v>
       </c>
-      <c r="B147" s="14" t="s">
+      <c r="B148" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="C148" s="15" t="s">
         <v>734</v>
       </c>
-      <c r="D147" s="14" t="s">
+      <c r="D148" s="14" t="s">
         <v>735</v>
       </c>
-      <c r="E147" s="31"/>
-    </row>
-    <row r="148" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A148" s="28" t="s">
+      <c r="E148" s="31"/>
+    </row>
+    <row r="149" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A149" s="28" t="s">
         <v>736</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B149" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="C149" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D149" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="E148" s="31"/>
-    </row>
-    <row r="149" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A149" s="28" t="s">
+      <c r="E149" s="31"/>
+    </row>
+    <row r="150" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="28" t="s">
         <v>740</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>742</v>
-      </c>
-      <c r="E149" s="31"/>
-    </row>
-    <row r="150" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A150" s="28" t="s">
-        <v>743</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E150" s="31"/>
     </row>
-    <row r="151" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A151" s="28" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C151" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="E151" s="31"/>
+    </row>
+    <row r="152" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A152" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C152" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D152" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="E151" s="31"/>
-    </row>
-    <row r="152" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A152" s="28" t="s">
+      <c r="E152" s="31"/>
+    </row>
+    <row r="153" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A153" s="28" t="s">
         <v>749</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B153" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C153" s="7" t="s">
         <v>750</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D153" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="E152" s="31"/>
-    </row>
-    <row r="153" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A153" s="30" t="s">
+      <c r="E153" s="31"/>
+    </row>
+    <row r="154" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A154" s="30" t="s">
         <v>752</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B154" s="16" t="s">
         <v>753</v>
       </c>
-      <c r="C153" s="17" t="s">
+      <c r="C154" s="17" t="s">
         <v>754</v>
       </c>
-      <c r="D153" s="16" t="s">
+      <c r="D154" s="16" t="s">
         <v>755</v>
       </c>
-      <c r="E153" s="31"/>
-    </row>
-    <row r="154" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A154" s="30" t="s">
+      <c r="E154" s="31"/>
+    </row>
+    <row r="155" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A155" s="30" t="s">
         <v>756</v>
       </c>
-      <c r="B154" s="16" t="s">
+      <c r="B155" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C154" s="17" t="s">
+      <c r="C155" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="D154" s="16" t="s">
+      <c r="D155" s="16" t="s">
         <v>758</v>
       </c>
-      <c r="E154" s="31"/>
-    </row>
-    <row r="155" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A155" s="30" t="s">
+      <c r="E155" s="31"/>
+    </row>
+    <row r="156" spans="1:5" ht="76" x14ac:dyDescent="0.25">
+      <c r="A156" s="30" t="s">
         <v>759</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B156" s="16" t="s">
         <v>760</v>
       </c>
-      <c r="C155" s="17" t="s">
+      <c r="C156" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D156" s="6" t="s">
         <v>762</v>
       </c>
-      <c r="E155" s="31"/>
-    </row>
-    <row r="156" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A156" s="30" t="s">
+      <c r="E156" s="31"/>
+    </row>
+    <row r="157" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A157" s="30" t="s">
         <v>763</v>
       </c>
-      <c r="B156" s="16" t="s">
+      <c r="B157" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C156" s="17" t="s">
+      <c r="C157" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D157" s="16" t="s">
         <v>765</v>
       </c>
-      <c r="E156" s="31"/>
-    </row>
-    <row r="157" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A157" s="28" t="s">
+      <c r="E157" s="31"/>
+    </row>
+    <row r="158" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="28" t="s">
         <v>766</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B158" s="6" t="s">
         <v>767</v>
       </c>
-      <c r="C157" s="7" t="s">
+      <c r="C158" s="7" t="s">
         <v>768</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D158" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="E157" s="29"/>
-    </row>
-    <row r="158" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A158" s="28" t="s">
+      <c r="E158" s="29"/>
+    </row>
+    <row r="159" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+      <c r="A159" s="28" t="s">
         <v>770</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B159" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C158" s="7" t="s">
+      <c r="C159" s="7" t="s">
         <v>771</v>
       </c>
-      <c r="D158" s="39" t="s">
+      <c r="D159" s="39" t="s">
         <v>772</v>
       </c>
-      <c r="E158" s="29"/>
-    </row>
-    <row r="159" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A159" s="28" t="s">
+      <c r="E159" s="29"/>
+    </row>
+    <row r="160" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A160" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B160" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C159" s="7" t="s">
+      <c r="C160" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="D159" s="39" t="s">
+      <c r="D160" s="39" t="s">
         <v>775</v>
       </c>
-      <c r="E159" s="29"/>
-    </row>
-    <row r="160" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A160" s="28" t="s">
+      <c r="E160" s="29"/>
+    </row>
+    <row r="161" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A161" s="28" t="s">
         <v>776</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B161" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C161" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D161" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="E160" s="40"/>
-    </row>
-    <row r="161" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A161" s="28" t="s">
+      <c r="E161" s="40"/>
+    </row>
+    <row r="162" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A162" s="28" t="s">
         <v>780</v>
       </c>
-      <c r="B161" s="6">
+      <c r="B162" s="6">
         <v>0</v>
       </c>
-      <c r="C161" s="7" t="s">
+      <c r="C162" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="D161" s="6" t="s">
+      <c r="D162" s="6" t="s">
         <v>782</v>
       </c>
-      <c r="E161" s="40"/>
-    </row>
-    <row r="162" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A162" s="28" t="s">
+      <c r="E162" s="40"/>
+    </row>
+    <row r="163" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A163" s="28" t="s">
         <v>783</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B163" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="C162" s="7" t="s">
+      <c r="C163" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D163" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="E162" s="40"/>
-    </row>
-    <row r="163" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A163" s="28" t="s">
+      <c r="E163" s="40"/>
+    </row>
+    <row r="164" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A164" s="28" t="s">
         <v>787</v>
       </c>
-      <c r="B163" s="6">
+      <c r="B164" s="6">
         <v>0</v>
       </c>
-      <c r="C163" s="7" t="s">
+      <c r="C164" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="D163" s="6"/>
-      <c r="E163" s="40"/>
-    </row>
-    <row r="164" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A164" s="41" t="s">
+      <c r="D164" s="6"/>
+      <c r="E164" s="40"/>
+    </row>
+    <row r="165" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="41" t="s">
         <v>789</v>
-      </c>
-      <c r="B164" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C164" s="42" t="s">
-        <v>790</v>
-      </c>
-      <c r="D164" s="25" t="s">
-        <v>791</v>
-      </c>
-      <c r="E164" s="40"/>
-    </row>
-    <row r="165" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A165" s="41" t="s">
-        <v>792</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>128</v>
       </c>
       <c r="C165" s="42" t="s">
+        <v>790</v>
+      </c>
+      <c r="D165" s="25" t="s">
+        <v>791</v>
+      </c>
+      <c r="E165" s="40"/>
+    </row>
+    <row r="166" spans="1:5" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A166" s="41" t="s">
+        <v>792</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C166" s="42" t="s">
         <v>793</v>
       </c>
-      <c r="D165" s="25" t="s">
+      <c r="D166" s="25" t="s">
         <v>794</v>
       </c>
-      <c r="E165" s="40" t="s">
+      <c r="E166" s="40" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A166" s="41" t="s">
+    <row r="167" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A167" s="41" t="s">
         <v>796</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>797</v>
-      </c>
-      <c r="C166" s="42" t="s">
-        <v>652</v>
-      </c>
-      <c r="D166" s="25" t="s">
-        <v>798</v>
-      </c>
-      <c r="E166" s="40"/>
-    </row>
-    <row r="167" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A167" s="41" t="s">
-        <v>799</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>797</v>
       </c>
       <c r="C167" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="D167" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="E167" s="40"/>
+    </row>
+    <row r="168" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A168" s="41" t="s">
+        <v>799</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="C168" s="42" t="s">
         <v>655</v>
       </c>
-      <c r="D167" s="25"/>
-      <c r="E167" s="40"/>
-    </row>
-    <row r="168" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A168" s="41" t="s">
+      <c r="D168" s="25"/>
+      <c r="E168" s="40"/>
+    </row>
+    <row r="169" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A169" s="41" t="s">
         <v>800</v>
       </c>
-      <c r="B168" s="12" t="s">
+      <c r="B169" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C168" s="42" t="s">
+      <c r="C169" s="42" t="s">
         <v>801</v>
       </c>
-      <c r="D168" s="25" t="s">
+      <c r="D169" s="25" t="s">
         <v>802</v>
       </c>
-      <c r="E168" s="40"/>
-    </row>
-    <row r="169" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A169" s="41" t="s">
+      <c r="E169" s="40"/>
+    </row>
+    <row r="170" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A170" s="41" t="s">
         <v>803</v>
       </c>
-      <c r="B169" s="12" t="s">
+      <c r="B170" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="C169" s="42" t="s">
+      <c r="C170" s="42" t="s">
         <v>805</v>
       </c>
-      <c r="D169" s="12" t="s">
+      <c r="D170" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="E169" s="43"/>
-    </row>
-    <row r="170" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A170" s="41" t="s">
+      <c r="E170" s="43"/>
+    </row>
+    <row r="171" spans="1:5" ht="88" x14ac:dyDescent="0.25">
+      <c r="A171" s="41" t="s">
         <v>807</v>
       </c>
-      <c r="B170" s="12" t="s">
+      <c r="B171" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C170" s="42" t="s">
+      <c r="C171" s="42" t="s">
         <v>808</v>
       </c>
-      <c r="D170" s="12" t="s">
+      <c r="D171" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="E170" s="43"/>
-    </row>
-    <row r="171" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A171" s="44" t="s">
+      <c r="E171" s="43"/>
+    </row>
+    <row r="172" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A172" s="44" t="s">
         <v>810</v>
-      </c>
-      <c r="B171" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C171" s="45" t="s">
-        <v>811</v>
-      </c>
-      <c r="D171" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="E171" s="40"/>
-    </row>
-    <row r="172" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A172" s="44" t="s">
-        <v>813</v>
       </c>
       <c r="B172" s="25" t="s">
         <v>111</v>
       </c>
       <c r="C172" s="45" t="s">
+        <v>811</v>
+      </c>
+      <c r="D172" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="E172" s="40"/>
+    </row>
+    <row r="173" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A173" s="44" t="s">
+        <v>813</v>
+      </c>
+      <c r="B173" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C173" s="45" t="s">
         <v>814</v>
       </c>
-      <c r="D172" s="25" t="s">
+      <c r="D173" s="25" t="s">
         <v>815</v>
       </c>
-      <c r="E172" s="40"/>
-    </row>
-    <row r="173" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A173" s="28" t="s">
+      <c r="E173" s="40"/>
+    </row>
+    <row r="174" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A174" s="28" t="s">
         <v>816</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C173" s="15" t="s">
-        <v>817</v>
-      </c>
-      <c r="D173" s="14" t="s">
-        <v>818</v>
-      </c>
-      <c r="E173" s="29"/>
-    </row>
-    <row r="174" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A174" s="28" t="s">
-        <v>819</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C174" s="7" t="s">
+      <c r="C174" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="D174" s="14" t="s">
+        <v>818</v>
+      </c>
+      <c r="E174" s="29"/>
+    </row>
+    <row r="175" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A175" s="28" t="s">
+        <v>819</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C175" s="7" t="s">
         <v>741</v>
       </c>
-      <c r="D174" s="6" t="s">
+      <c r="D175" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="E174" s="29"/>
-    </row>
-    <row r="175" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A175" s="28" t="s">
+      <c r="E175" s="29"/>
+    </row>
+    <row r="176" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A176" s="28" t="s">
         <v>821</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B176" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C175" s="7" t="s">
+      <c r="C176" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="D175" s="6"/>
-      <c r="E175" s="29"/>
-    </row>
-    <row r="176" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A176" s="28" t="s">
+      <c r="D176" s="6"/>
+      <c r="E176" s="29"/>
+    </row>
+    <row r="177" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="28" t="s">
         <v>823</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B177" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C176" s="7" t="s">
+      <c r="C177" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="D176" s="6" t="s">
+      <c r="D177" s="6" t="s">
         <v>825</v>
       </c>
-      <c r="E176" s="29" t="s">
+      <c r="E177" s="29" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A177" s="28" t="s">
+    <row r="178" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="28" t="s">
         <v>827</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B178" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C177" s="7" t="s">
+      <c r="C178" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="D177" s="6" t="s">
+      <c r="D178" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="E177" s="29" t="s">
+      <c r="E178" s="29" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A178" s="28" t="s">
+    <row r="179" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A179" s="28" t="s">
         <v>831</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B179" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C178" s="7" t="s">
+      <c r="C179" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="D178" s="6" t="s">
+      <c r="D179" s="6" t="s">
         <v>833</v>
       </c>
-      <c r="E178" s="29"/>
-    </row>
-    <row r="179" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A179" s="28" t="s">
+      <c r="E179" s="29"/>
+    </row>
+    <row r="180" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="A180" s="28" t="s">
         <v>834</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C179" s="15" t="s">
-        <v>835</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>836</v>
-      </c>
-      <c r="E179" s="29"/>
-    </row>
-    <row r="180" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A180" s="28" t="s">
-        <v>837</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C180" s="7" t="s">
+      <c r="C180" s="15" t="s">
+        <v>835</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>836</v>
+      </c>
+      <c r="E180" s="29"/>
+    </row>
+    <row r="181" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A181" s="28" t="s">
+        <v>837</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C181" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="D180" s="6" t="s">
+      <c r="D181" s="6" t="s">
         <v>839</v>
       </c>
-      <c r="E180" s="29"/>
-    </row>
-    <row r="181" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A181" s="28" t="s">
+      <c r="E181" s="29"/>
+    </row>
+    <row r="182" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A182" s="28" t="s">
         <v>840</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="D181" s="6" t="s">
-        <v>842</v>
-      </c>
-      <c r="E181" s="29"/>
-    </row>
-    <row r="182" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A182" s="28" t="s">
-        <v>843</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>584</v>
       </c>
       <c r="C182" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="E182" s="29"/>
+    </row>
+    <row r="183" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A183" s="28" t="s">
+        <v>843</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C183" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="D182" s="6" t="s">
+      <c r="D183" s="6" t="s">
         <v>845</v>
       </c>
-      <c r="E182" s="29"/>
-    </row>
-    <row r="183" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A183" s="28" t="s">
+      <c r="E183" s="29"/>
+    </row>
+    <row r="184" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A184" s="28" t="s">
         <v>846</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>848</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E183" s="29"/>
-    </row>
-    <row r="184" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A184" s="28" t="s">
-        <v>850</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>847</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E184" s="29"/>
     </row>
-    <row r="185" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A185" s="28" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>847</v>
       </c>
       <c r="C185" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E185" s="29"/>
+    </row>
+    <row r="186" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A186" s="28" t="s">
+        <v>853</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="C186" s="7" t="s">
         <v>854</v>
       </c>
-      <c r="D185" s="6" t="s">
+      <c r="D186" s="6" t="s">
         <v>855</v>
       </c>
-      <c r="E185" s="29"/>
-    </row>
-    <row r="186" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A186" s="28" t="s">
+      <c r="E186" s="29"/>
+    </row>
+    <row r="187" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A187" s="28" t="s">
         <v>856</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="B187" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C186" s="7" t="s">
+      <c r="C187" s="7" t="s">
         <v>857</v>
       </c>
-      <c r="D186" s="6" t="s">
+      <c r="D187" s="6" t="s">
         <v>858</v>
       </c>
-      <c r="E186" s="29"/>
-    </row>
-    <row r="187" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A187" s="28" t="s">
+      <c r="E187" s="29"/>
+    </row>
+    <row r="188" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A188" s="28" t="s">
         <v>859</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="D187" s="6"/>
-      <c r="E187" s="29"/>
-    </row>
-    <row r="188" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A188" s="28" t="s">
-        <v>862</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>860</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="29"/>
     </row>
-    <row r="189" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A189" s="28" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>860</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D189" s="6"/>
       <c r="E189" s="29"/>
     </row>
-    <row r="190" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A190" s="28" t="s">
+        <v>864</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="D190" s="6"/>
+      <c r="E190" s="29"/>
+    </row>
+    <row r="191" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A191" s="28" t="s">
         <v>866</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>860</v>
-      </c>
-      <c r="C190" s="10" t="s">
-        <v>867</v>
-      </c>
-      <c r="D190" s="9" t="s">
-        <v>868</v>
-      </c>
-      <c r="E190" s="36"/>
-    </row>
-    <row r="191" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A191" s="28" t="s">
-        <v>869</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>860</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D191" s="9" t="s">
         <v>868</v>
       </c>
       <c r="E191" s="36"/>
     </row>
-    <row r="192" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A192" s="28" t="s">
+        <v>869</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="E192" s="36"/>
+    </row>
+    <row r="193" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A193" s="28" t="s">
         <v>871</v>
       </c>
-      <c r="B192" s="6" t="s">
+      <c r="B193" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="C192" s="7" t="s">
+      <c r="C193" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="D192" s="6"/>
-      <c r="E192" s="29"/>
-    </row>
-    <row r="193" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A193" s="28" t="s">
+      <c r="D193" s="6"/>
+      <c r="E193" s="29"/>
+    </row>
+    <row r="194" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A194" s="28" t="s">
         <v>873</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B194" s="9" t="s">
         <v>860</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C194" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="D193" s="9" t="s">
+      <c r="D194" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="E193" s="36"/>
-    </row>
-    <row r="194" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A194" s="28" t="s">
+      <c r="E194" s="36"/>
+    </row>
+    <row r="195" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A195" s="28" t="s">
         <v>875</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B195" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="C195" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="D194" s="6"/>
-      <c r="E194" s="29"/>
-    </row>
-    <row r="195" spans="1:5" ht="102" x14ac:dyDescent="0.2">
-      <c r="A195" s="28" t="s">
+      <c r="D195" s="6"/>
+      <c r="E195" s="29"/>
+    </row>
+    <row r="196" spans="1:5" ht="100" x14ac:dyDescent="0.25">
+      <c r="A196" s="28" t="s">
         <v>876</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B196" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="C195" s="7" t="s">
+      <c r="C196" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="D195" s="6" t="s">
+      <c r="D196" s="6" t="s">
         <v>879</v>
       </c>
-      <c r="E195" s="29"/>
-    </row>
-    <row r="196" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A196" s="28" t="s">
+      <c r="E196" s="29"/>
+    </row>
+    <row r="197" spans="1:5" ht="75.5" x14ac:dyDescent="0.25">
+      <c r="A197" s="28" t="s">
         <v>880</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>881</v>
-      </c>
-      <c r="D196" s="6" t="s">
-        <v>882</v>
-      </c>
-      <c r="E196" s="29"/>
-    </row>
-    <row r="197" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A197" s="28" t="s">
-        <v>883</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="E197" s="29"/>
     </row>
-    <row r="198" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A198" s="28" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="E198" s="29"/>
+    </row>
+    <row r="199" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A199" s="28" t="s">
+        <v>886</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C199" s="7" t="s">
         <v>887</v>
       </c>
-      <c r="D198" s="6" t="s">
+      <c r="D199" s="6" t="s">
         <v>888</v>
       </c>
-      <c r="E198" s="29"/>
-    </row>
-    <row r="199" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A199" s="28" t="s">
+      <c r="E199" s="29"/>
+    </row>
+    <row r="200" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A200" s="28" t="s">
         <v>889</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>890</v>
-      </c>
-      <c r="D199" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="E199" s="29"/>
-    </row>
-    <row r="200" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A200" s="28" t="s">
-        <v>892</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C200" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="E200" s="29"/>
+    </row>
+    <row r="201" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A201" s="28" t="s">
+        <v>892</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C201" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="D200" s="6" t="s">
+      <c r="D201" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="E200" s="29"/>
-    </row>
-    <row r="201" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A201" s="28" t="s">
+      <c r="E201" s="29"/>
+    </row>
+    <row r="202" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A202" s="28" t="s">
         <v>895</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="E201" s="29"/>
-    </row>
-    <row r="202" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A202" s="28" t="s">
-        <v>899</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>896</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="E202" s="29"/>
+    </row>
+    <row r="203" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A203" s="28" t="s">
+        <v>899</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="C203" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="D202" s="6" t="s">
+      <c r="D203" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="E202" s="29"/>
-    </row>
-    <row r="203" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A203" s="28" t="s">
+      <c r="E203" s="29"/>
+    </row>
+    <row r="204" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A204" s="28" t="s">
         <v>902</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="E203" s="29"/>
-    </row>
-    <row r="204" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A204" s="28" t="s">
-        <v>905</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>128</v>
@@ -12871,13 +12880,13 @@
         <v>903</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>451</v>
+        <v>904</v>
       </c>
       <c r="E204" s="29"/>
     </row>
-    <row r="205" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A205" s="28" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>128</v>
@@ -12890,24 +12899,24 @@
       </c>
       <c r="E205" s="29"/>
     </row>
-    <row r="206" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A206" s="28" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>451</v>
       </c>
       <c r="E206" s="29"/>
     </row>
-    <row r="207" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A207" s="28" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>128</v>
@@ -12920,54 +12929,69 @@
       </c>
       <c r="E207" s="29"/>
     </row>
-    <row r="208" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A208" s="28" t="s">
+        <v>909</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E208" s="29"/>
+    </row>
+    <row r="209" spans="1:5" ht="88.5" x14ac:dyDescent="0.25">
+      <c r="A209" s="28" t="s">
         <v>910</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B209" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C208" s="7" t="s">
+      <c r="C209" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="D208" s="6" t="s">
+      <c r="D209" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="E208" s="29"/>
-    </row>
-    <row r="209" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A209" s="30" t="s">
+      <c r="E209" s="29"/>
+    </row>
+    <row r="210" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A210" s="30" t="s">
         <v>913</v>
       </c>
-      <c r="B209" s="16" t="s">
+      <c r="B210" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C209" s="17" t="s">
+      <c r="C210" s="17" t="s">
         <v>914</v>
       </c>
-      <c r="D209" s="16"/>
-      <c r="E209" s="46"/>
-    </row>
-    <row r="210" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A210" s="30"/>
-      <c r="B210" s="16"/>
-      <c r="C210" s="17"/>
       <c r="D210" s="16"/>
       <c r="E210" s="46"/>
     </row>
-    <row r="211" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A211" s="30"/>
       <c r="B211" s="16"/>
       <c r="C211" s="17"/>
       <c r="D211" s="16"/>
       <c r="E211" s="46"/>
     </row>
-    <row r="212" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="A212" s="30"/>
       <c r="B212" s="16"/>
       <c r="C212" s="17"/>
       <c r="D212" s="16"/>
       <c r="E212" s="46"/>
+    </row>
+    <row r="213" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A213" s="30"/>
+      <c r="B213" s="16"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="16"/>
+      <c r="E213" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -12981,14 +13005,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="29.81640625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
         <v>915</v>
       </c>
@@ -12999,14 +13023,14 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="81" t="s">
         <v>917</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
-    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -13017,7 +13041,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>16</v>
       </c>
@@ -13028,7 +13052,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>16</v>
       </c>
@@ -13039,7 +13063,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>16</v>
       </c>
@@ -13050,7 +13074,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>16</v>
       </c>
@@ -13061,32 +13085,32 @@
         <v>921</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
     </row>
-    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
     </row>
-    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
     </row>
-    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -13106,14 +13130,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C147"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="91.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7265625" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" customWidth="1"/>
+    <col min="3" max="3" width="91.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
         <v>922</v>
       </c>
@@ -13124,14 +13148,14 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="83" t="s">
         <v>924</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
-    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>0</v>
       </c>
@@ -13143,7 +13167,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="48">
         <v>128</v>
       </c>
@@ -13155,7 +13179,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>150</v>
       </c>
@@ -13167,7 +13191,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>151</v>
       </c>
@@ -13177,7 +13201,7 @@
       </c>
       <c r="C6" s="35"/>
     </row>
-    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>152</v>
       </c>
@@ -13187,7 +13211,7 @@
       </c>
       <c r="C7" s="35"/>
     </row>
-    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>153</v>
       </c>
@@ -13199,7 +13223,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>169</v>
       </c>
@@ -13209,7 +13233,7 @@
       </c>
       <c r="C9" s="35"/>
     </row>
-    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>171</v>
       </c>
@@ -13219,7 +13243,7 @@
       </c>
       <c r="C10" s="35"/>
     </row>
-    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>172</v>
       </c>
@@ -13229,7 +13253,7 @@
       </c>
       <c r="C11" s="35"/>
     </row>
-    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>173</v>
       </c>
@@ -13239,7 +13263,7 @@
       </c>
       <c r="C12" s="35"/>
     </row>
-    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>256</v>
       </c>
@@ -13251,7 +13275,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>276</v>
       </c>
@@ -13261,7 +13285,7 @@
       </c>
       <c r="C14" s="35"/>
     </row>
-    <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>277</v>
       </c>
@@ -13271,7 +13295,7 @@
       </c>
       <c r="C15" s="35"/>
     </row>
-    <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>333</v>
       </c>
@@ -13281,7 +13305,7 @@
       </c>
       <c r="C16" s="35"/>
     </row>
-    <row r="17" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>339</v>
       </c>
@@ -13291,7 +13315,7 @@
       </c>
       <c r="C17" s="35"/>
     </row>
-    <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>386</v>
       </c>
@@ -13303,7 +13327,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>387</v>
       </c>
@@ -13313,7 +13337,7 @@
       </c>
       <c r="C19" s="35"/>
     </row>
-    <row r="20" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>388</v>
       </c>
@@ -13323,7 +13347,7 @@
       </c>
       <c r="C20" s="35"/>
     </row>
-    <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>389</v>
       </c>
@@ -13333,7 +13357,7 @@
       </c>
       <c r="C21" s="35"/>
     </row>
-    <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>390</v>
       </c>
@@ -13343,7 +13367,7 @@
       </c>
       <c r="C22" s="35"/>
     </row>
-    <row r="23" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>527</v>
       </c>
@@ -13355,7 +13379,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>528</v>
       </c>
@@ -13365,7 +13389,7 @@
       </c>
       <c r="C24" s="35"/>
     </row>
-    <row r="25" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>532</v>
       </c>
@@ -13375,7 +13399,7 @@
       </c>
       <c r="C25" s="35"/>
     </row>
-    <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>537</v>
       </c>
@@ -13387,7 +13411,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>1024</v>
       </c>
@@ -13399,7 +13423,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>1025</v>
       </c>
@@ -13411,7 +13435,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>1026</v>
       </c>
@@ -13423,7 +13447,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>1029</v>
       </c>
@@ -13433,7 +13457,7 @@
       </c>
       <c r="C30" s="35"/>
     </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1044</v>
       </c>
@@ -13445,7 +13469,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>1063</v>
       </c>
@@ -13457,7 +13481,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1152</v>
       </c>
@@ -13469,7 +13493,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="34">
         <v>1153</v>
       </c>
@@ -13481,7 +13505,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1174</v>
       </c>
@@ -13493,7 +13517,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="34">
         <v>1175</v>
       </c>
@@ -13505,7 +13529,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1177</v>
       </c>
@@ -13517,7 +13541,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="34">
         <v>1195</v>
       </c>
@@ -13529,7 +13553,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1197</v>
       </c>
@@ -13541,7 +13565,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="34">
         <v>1280</v>
       </c>
@@ -13553,7 +13577,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1300</v>
       </c>
@@ -13565,7 +13589,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
         <v>1363</v>
       </c>
@@ -13577,7 +13601,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="34">
         <v>1551</v>
       </c>
@@ -13589,7 +13613,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A44" s="34">
         <v>1556</v>
       </c>
@@ -13601,7 +13625,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="34">
         <v>1557</v>
       </c>
@@ -13613,7 +13637,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="34">
         <v>1561</v>
       </c>
@@ -13625,7 +13649,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A47" s="34">
         <v>2049</v>
       </c>
@@ -13637,7 +13661,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="48">
         <v>2176</v>
       </c>
@@ -13649,7 +13673,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A49" s="34">
         <v>2199</v>
       </c>
@@ -13661,7 +13685,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A50" s="34">
         <v>2219</v>
       </c>
@@ -13673,7 +13697,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A51" s="34">
         <v>2221</v>
       </c>
@@ -13685,7 +13709,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="48">
         <v>2304</v>
       </c>
@@ -13697,7 +13721,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A53" s="34">
         <v>2324</v>
       </c>
@@ -13709,7 +13733,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="14">
         <v>2434</v>
       </c>
@@ -13721,7 +13745,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="14">
         <v>2437</v>
       </c>
@@ -13733,7 +13757,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="34">
         <v>2580</v>
       </c>
@@ -13745,7 +13769,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="34">
         <v>2585</v>
       </c>
@@ -13757,7 +13781,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A58" s="14">
         <v>4224</v>
       </c>
@@ -13769,7 +13793,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A59" s="14">
         <v>6876</v>
       </c>
@@ -13781,7 +13805,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A60" s="34">
         <v>9119</v>
       </c>
@@ -13791,7 +13815,7 @@
       </c>
       <c r="C60" s="35"/>
     </row>
-    <row r="61" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="14">
         <v>10240</v>
       </c>
@@ -13803,7 +13827,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A62" s="34">
         <v>12282</v>
       </c>
@@ -13813,7 +13837,7 @@
       </c>
       <c r="C62" s="35"/>
     </row>
-    <row r="63" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="34">
         <v>13312</v>
       </c>
@@ -13823,7 +13847,7 @@
       </c>
       <c r="C63" s="35"/>
     </row>
-    <row r="64" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A64" s="34">
         <v>14464</v>
       </c>
@@ -13833,7 +13857,7 @@
       </c>
       <c r="C64" s="35"/>
     </row>
-    <row r="65" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A65" s="14">
         <v>16383</v>
       </c>
@@ -13845,7 +13869,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="34">
         <v>16512</v>
       </c>
@@ -13855,7 +13879,7 @@
       </c>
       <c r="C66" s="35"/>
     </row>
-    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A67" s="34">
         <v>16514</v>
       </c>
@@ -13865,7 +13889,7 @@
       </c>
       <c r="C67" s="35"/>
     </row>
-    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="34">
         <v>16534</v>
       </c>
@@ -13875,7 +13899,7 @@
       </c>
       <c r="C68" s="35"/>
     </row>
-    <row r="69" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A69" s="34">
         <v>16535</v>
       </c>
@@ -13885,7 +13909,7 @@
       </c>
       <c r="C69" s="35"/>
     </row>
-    <row r="70" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A70" s="34">
         <v>16640</v>
       </c>
@@ -13895,7 +13919,7 @@
       </c>
       <c r="C70" s="35"/>
     </row>
-    <row r="71" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A71" s="34">
         <v>16661</v>
       </c>
@@ -13905,7 +13929,7 @@
       </c>
       <c r="C71" s="35"/>
     </row>
-    <row r="72" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A72" s="34">
         <v>16770</v>
       </c>
@@ -13915,7 +13939,7 @@
       </c>
       <c r="C72" s="35"/>
     </row>
-    <row r="73" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A73" s="34">
         <v>16773</v>
       </c>
@@ -13925,7 +13949,7 @@
       </c>
       <c r="C73" s="35"/>
     </row>
-    <row r="74" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A74" s="34">
         <v>16832</v>
       </c>
@@ -13935,7 +13959,7 @@
       </c>
       <c r="C74" s="35"/>
     </row>
-    <row r="75" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A75" s="34">
         <v>16916</v>
       </c>
@@ -13945,7 +13969,7 @@
       </c>
       <c r="C75" s="35"/>
     </row>
-    <row r="76" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A76" s="34">
         <v>16921</v>
       </c>
@@ -13955,7 +13979,7 @@
       </c>
       <c r="C76" s="35"/>
     </row>
-    <row r="77" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A77" s="34">
         <v>17409</v>
       </c>
@@ -13965,7 +13989,7 @@
       </c>
       <c r="C77" s="35"/>
     </row>
-    <row r="78" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="34">
         <v>17410</v>
       </c>
@@ -13975,7 +13999,7 @@
       </c>
       <c r="C78" s="35"/>
     </row>
-    <row r="79" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="34">
         <v>17536</v>
       </c>
@@ -13985,7 +14009,7 @@
       </c>
       <c r="C79" s="35"/>
     </row>
-    <row r="80" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A80" s="34">
         <v>17558</v>
       </c>
@@ -13995,7 +14019,7 @@
       </c>
       <c r="C80" s="35"/>
     </row>
-    <row r="81" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A81" s="34">
         <v>17945</v>
       </c>
@@ -14005,7 +14029,7 @@
       </c>
       <c r="C81" s="35"/>
     </row>
-    <row r="82" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A82" s="34">
         <v>18560</v>
       </c>
@@ -14015,7 +14039,7 @@
       </c>
       <c r="C82" s="35"/>
     </row>
-    <row r="83" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A83" s="34">
         <v>18708</v>
       </c>
@@ -14025,7 +14049,7 @@
       </c>
       <c r="C83" s="35"/>
     </row>
-    <row r="84" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A84" s="34">
         <v>18818</v>
       </c>
@@ -14035,7 +14059,7 @@
       </c>
       <c r="C84" s="35"/>
     </row>
-    <row r="85" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A85" s="34">
         <v>18969</v>
       </c>
@@ -14045,7 +14069,7 @@
       </c>
       <c r="C85" s="35"/>
     </row>
-    <row r="86" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A86" s="14">
         <v>23260</v>
       </c>
@@ -14057,7 +14081,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A87" s="14">
         <v>32896</v>
       </c>
@@ -14069,7 +14093,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A88" s="34">
         <v>32918</v>
       </c>
@@ -14081,7 +14105,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A89" s="14">
         <v>32921</v>
       </c>
@@ -14093,7 +14117,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A90" s="34">
         <v>33044</v>
       </c>
@@ -14103,7 +14127,7 @@
       </c>
       <c r="C90" s="35"/>
     </row>
-    <row r="91" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A91" s="34">
         <v>33107</v>
       </c>
@@ -14115,7 +14139,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A92" s="34">
         <v>33154</v>
       </c>
@@ -14127,7 +14151,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A93" s="34">
         <v>33157</v>
       </c>
@@ -14139,7 +14163,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A94" s="34">
         <v>33300</v>
       </c>
@@ -14151,7 +14175,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A95" s="34">
         <v>33305</v>
       </c>
@@ -14163,7 +14187,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A96" s="34">
         <v>33793</v>
       </c>
@@ -14175,7 +14199,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A97" s="34">
         <v>33794</v>
       </c>
@@ -14187,7 +14211,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A98" s="14">
         <v>33921</v>
       </c>
@@ -14199,7 +14223,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A99" s="34">
         <v>33943</v>
       </c>
@@ -14211,7 +14235,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A100" s="34">
         <v>34319</v>
       </c>
@@ -14223,7 +14247,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A101" s="34">
         <v>34329</v>
       </c>
@@ -14235,7 +14259,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A102" s="14">
         <v>39644</v>
       </c>
@@ -14247,7 +14271,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A103" s="34">
         <v>49280</v>
       </c>
@@ -14259,7 +14283,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A104" s="34">
         <v>49302</v>
       </c>
@@ -14271,7 +14295,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A105" s="34">
         <v>49538</v>
       </c>
@@ -14283,7 +14307,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A106" s="34">
         <v>49541</v>
       </c>
@@ -14295,7 +14319,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A107" s="34">
         <v>49689</v>
       </c>
@@ -14307,7 +14331,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A108" s="34">
         <v>50177</v>
       </c>
@@ -14319,7 +14343,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A109" s="14">
         <v>56028</v>
       </c>
@@ -14331,7 +14355,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A110" s="34">
         <v>67584</v>
       </c>
@@ -14343,7 +14367,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A111" s="34">
         <v>67840</v>
       </c>
@@ -14355,7 +14379,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A112" s="34">
         <v>131604</v>
       </c>
@@ -14365,7 +14389,7 @@
       </c>
       <c r="C112" s="35"/>
     </row>
-    <row r="113" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A113" s="34">
         <v>132097</v>
       </c>
@@ -14375,7 +14399,7 @@
       </c>
       <c r="C113" s="35"/>
     </row>
-    <row r="114" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A114" s="34">
         <v>262272</v>
       </c>
@@ -14385,7 +14409,7 @@
       </c>
       <c r="C114" s="35"/>
     </row>
-    <row r="115" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A115" s="34">
         <v>262533</v>
       </c>
@@ -14395,7 +14419,7 @@
       </c>
       <c r="C115" s="35"/>
     </row>
-    <row r="116" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A116" s="34">
         <v>262676</v>
       </c>
@@ -14405,7 +14429,7 @@
       </c>
       <c r="C116" s="35"/>
     </row>
-    <row r="117" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A117" s="34">
         <v>262681</v>
       </c>
@@ -14415,7 +14439,7 @@
       </c>
       <c r="C117" s="35"/>
     </row>
-    <row r="118" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A118" s="34">
         <v>524416</v>
       </c>
@@ -14425,7 +14449,7 @@
       </c>
       <c r="C118" s="35"/>
     </row>
-    <row r="119" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A119" s="34">
         <v>524674</v>
       </c>
@@ -14435,7 +14459,7 @@
       </c>
       <c r="C119" s="35"/>
     </row>
-    <row r="120" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A120" s="34">
         <v>524675</v>
       </c>
@@ -14445,7 +14469,7 @@
       </c>
       <c r="C120" s="35"/>
     </row>
-    <row r="121" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A121" s="34">
         <v>524677</v>
       </c>
@@ -14455,7 +14479,7 @@
       </c>
       <c r="C121" s="35"/>
     </row>
-    <row r="122" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A122" s="34">
         <v>524820</v>
       </c>
@@ -14465,7 +14489,7 @@
       </c>
       <c r="C122" s="35"/>
     </row>
-    <row r="123" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A123" s="34">
         <v>524825</v>
       </c>
@@ -14475,7 +14499,7 @@
       </c>
       <c r="C123" s="35"/>
     </row>
-    <row r="124" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A124" s="34">
         <v>525313</v>
       </c>
@@ -14485,7 +14509,7 @@
       </c>
       <c r="C124" s="35"/>
     </row>
-    <row r="125" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A125" s="34">
         <v>525314</v>
       </c>
@@ -14495,7 +14519,7 @@
       </c>
       <c r="C125" s="35"/>
     </row>
-    <row r="126" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A126" s="34">
         <v>525315</v>
       </c>
@@ -14505,7 +14529,7 @@
       </c>
       <c r="C126" s="35"/>
     </row>
-    <row r="127" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A127" s="34">
         <v>525844</v>
       </c>
@@ -14515,7 +14539,7 @@
       </c>
       <c r="C127" s="35"/>
     </row>
-    <row r="128" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A128" s="34">
         <v>540800</v>
       </c>
@@ -14525,7 +14549,7 @@
       </c>
       <c r="C128" s="35"/>
     </row>
-    <row r="129" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A129" s="34">
         <v>540825</v>
       </c>
@@ -14535,7 +14559,7 @@
       </c>
       <c r="C129" s="35"/>
     </row>
-    <row r="130" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A130" s="34">
         <v>541058</v>
       </c>
@@ -14545,7 +14569,7 @@
       </c>
       <c r="C130" s="35"/>
     </row>
-    <row r="131" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A131" s="34">
         <v>541209</v>
       </c>
@@ -14555,7 +14579,7 @@
       </c>
       <c r="C131" s="35"/>
     </row>
-    <row r="132" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A132" s="34">
         <v>541697</v>
       </c>
@@ -14565,7 +14589,7 @@
       </c>
       <c r="C132" s="35"/>
     </row>
-    <row r="133" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A133" s="34">
         <v>542233</v>
       </c>
@@ -14575,7 +14599,7 @@
       </c>
       <c r="C133" s="35"/>
     </row>
-    <row r="134" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A134" s="34">
         <v>542848</v>
       </c>
@@ -14585,7 +14609,7 @@
       </c>
       <c r="C134" s="35"/>
     </row>
-    <row r="135" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A135" s="14">
         <v>543106</v>
       </c>
@@ -14597,7 +14621,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A136" s="34">
         <v>543257</v>
       </c>
@@ -14607,7 +14631,7 @@
       </c>
       <c r="C136" s="35"/>
     </row>
-    <row r="137" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A137" s="14">
         <v>547548</v>
       </c>
@@ -14619,7 +14643,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A138" s="34">
         <v>558617</v>
       </c>
@@ -14629,7 +14653,7 @@
       </c>
       <c r="C138" s="35"/>
     </row>
-    <row r="139" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A139" s="14">
         <v>573568</v>
       </c>
@@ -14641,7 +14665,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A140" s="34">
         <v>573593</v>
       </c>
@@ -14651,7 +14675,7 @@
       </c>
       <c r="C140" s="35"/>
     </row>
-    <row r="141" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A141" s="34">
         <v>4194432</v>
       </c>
@@ -14661,7 +14685,7 @@
       </c>
       <c r="C141" s="35"/>
     </row>
-    <row r="142" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A142" s="34">
         <v>4194454</v>
       </c>
@@ -14671,7 +14695,7 @@
       </c>
       <c r="C142" s="35"/>
     </row>
-    <row r="143" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A143" s="34">
         <v>4194690</v>
       </c>
@@ -14681,7 +14705,7 @@
       </c>
       <c r="C143" s="35"/>
     </row>
-    <row r="144" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A144" s="34">
         <v>4194841</v>
       </c>
@@ -14691,7 +14715,7 @@
       </c>
       <c r="C144" s="35"/>
     </row>
-    <row r="145" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A145" s="34">
         <v>4195329</v>
       </c>
@@ -14701,7 +14725,7 @@
       </c>
       <c r="C145" s="35"/>
     </row>
-    <row r="146" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A146" s="34">
         <v>4196503</v>
       </c>
@@ -14711,7 +14735,7 @@
       </c>
       <c r="C146" s="35"/>
     </row>
-    <row r="147" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A147" s="34">
         <v>4196523</v>
       </c>
@@ -14736,14 +14760,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="3" width="39.42578125" customWidth="1"/>
-    <col min="4" max="4" width="54.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="3" width="39.453125" customWidth="1"/>
+    <col min="4" max="4" width="54.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>922</v>
       </c>
@@ -14757,7 +14781,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>336</v>
       </c>
@@ -14767,7 +14791,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -14781,7 +14805,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -14793,7 +14817,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>16</v>
       </c>
@@ -14805,7 +14829,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>64</v>
       </c>
@@ -14819,7 +14843,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>65</v>
       </c>
@@ -14833,7 +14857,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>67</v>
       </c>
@@ -14845,7 +14869,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>71</v>
       </c>
@@ -14857,7 +14881,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>80</v>
       </c>
@@ -14871,7 +14895,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>81</v>
       </c>
@@ -14885,7 +14909,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>88</v>
       </c>
@@ -14897,7 +14921,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>192</v>
       </c>
@@ -14909,7 +14933,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>193</v>
       </c>
@@ -14921,7 +14945,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>208</v>
       </c>
@@ -14933,7 +14957,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>256</v>
       </c>
@@ -14947,7 +14971,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>257</v>
       </c>
@@ -14961,7 +14985,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>259</v>
       </c>
@@ -14973,7 +14997,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>263</v>
       </c>
@@ -14985,7 +15009,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>272</v>
       </c>
@@ -14999,7 +15023,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>273</v>
       </c>
@@ -15011,7 +15035,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>320</v>
       </c>
@@ -15023,7 +15047,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>321</v>
       </c>
@@ -15035,7 +15059,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>464</v>
       </c>
@@ -15059,14 +15083,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="4" max="4" width="43.1796875" customWidth="1"/>
     <col min="11" max="11" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="51" t="s">
         <v>978</v>
       </c>
@@ -15101,7 +15125,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="54" t="s">
         <v>987</v>
       </c>
@@ -15134,7 +15158,7 @@
       </c>
       <c r="K2" s="56"/>
     </row>
-    <row r="3" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57"/>
       <c r="B3" s="55" t="s">
         <v>990</v>
@@ -15151,7 +15175,7 @@
       <c r="J3" s="58"/>
       <c r="K3" s="56"/>
     </row>
-    <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="54" t="s">
         <v>992</v>
       </c>
@@ -15184,7 +15208,7 @@
       </c>
       <c r="K4" s="56"/>
     </row>
-    <row r="5" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57"/>
       <c r="B5" s="55" t="s">
         <v>1000</v>
@@ -15201,7 +15225,7 @@
       <c r="J5" s="56"/>
       <c r="K5" s="56"/>
     </row>
-    <row r="6" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57"/>
       <c r="B6" s="55" t="s">
         <v>1002</v>
@@ -15218,7 +15242,7 @@
       <c r="J6" s="56"/>
       <c r="K6" s="56"/>
     </row>
-    <row r="7" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57"/>
       <c r="B7" s="55" t="s">
         <v>1004</v>
@@ -15235,7 +15259,7 @@
       <c r="J7" s="56"/>
       <c r="K7" s="56"/>
     </row>
-    <row r="8" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57"/>
       <c r="B8" s="55" t="s">
         <v>1006</v>
@@ -15252,7 +15276,7 @@
       <c r="J8" s="56"/>
       <c r="K8" s="56"/>
     </row>
-    <row r="9" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57"/>
       <c r="B9" s="55" t="s">
         <v>1008</v>
@@ -15269,7 +15293,7 @@
       <c r="J9" s="56"/>
       <c r="K9" s="56"/>
     </row>
-    <row r="10" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="55" t="s">
         <v>1010</v>
@@ -15288,7 +15312,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
         <v>1013</v>
       </c>
@@ -15321,7 +15345,7 @@
       </c>
       <c r="K11" s="56"/>
     </row>
-    <row r="12" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57"/>
       <c r="B12" s="55" t="s">
         <v>1017</v>
@@ -15338,7 +15362,7 @@
       <c r="J12" s="56"/>
       <c r="K12" s="56"/>
     </row>
-    <row r="13" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57"/>
       <c r="B13" s="55" t="s">
         <v>1019</v>
@@ -15355,7 +15379,7 @@
       <c r="J13" s="56"/>
       <c r="K13" s="56"/>
     </row>
-    <row r="14" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57"/>
       <c r="B14" s="55" t="s">
         <v>1021</v>
@@ -15372,7 +15396,7 @@
       <c r="J14" s="56"/>
       <c r="K14" s="56"/>
     </row>
-    <row r="15" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57"/>
       <c r="B15" s="55" t="s">
         <v>1023</v>
@@ -15389,7 +15413,7 @@
       <c r="J15" s="56"/>
       <c r="K15" s="56"/>
     </row>
-    <row r="16" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="63" t="s">
         <v>1025</v>
       </c>
@@ -15422,7 +15446,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57"/>
       <c r="B17" s="55" t="s">
         <v>1030</v>
@@ -15441,7 +15465,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="54" t="s">
         <v>1032</v>
       </c>
@@ -15474,7 +15498,7 @@
       </c>
       <c r="K18" s="56"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="55" t="s">
         <v>1035</v>
@@ -15491,7 +15515,7 @@
       <c r="J19" s="56"/>
       <c r="K19" s="56"/>
     </row>
-    <row r="20" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="55" t="s">
         <v>1037</v>
@@ -15508,7 +15532,7 @@
       <c r="J20" s="56"/>
       <c r="K20" s="56"/>
     </row>
-    <row r="21" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57"/>
       <c r="B21" s="55" t="s">
         <v>1039</v>
@@ -15525,7 +15549,7 @@
       <c r="J21" s="56"/>
       <c r="K21" s="56"/>
     </row>
-    <row r="22" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57"/>
       <c r="B22" s="55" t="s">
         <v>1041</v>
@@ -15542,7 +15566,7 @@
       <c r="J22" s="56"/>
       <c r="K22" s="56"/>
     </row>
-    <row r="23" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A23" s="63" t="s">
         <v>1043</v>
       </c>
@@ -15575,7 +15599,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57"/>
       <c r="B24" s="23">
         <v>8389906</v>
@@ -15594,7 +15618,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25" s="57"/>
       <c r="B25" s="23">
         <v>10487058</v>
@@ -15611,7 +15635,7 @@
       <c r="J25" s="56"/>
       <c r="K25" s="56"/>
     </row>
-    <row r="26" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A26" s="54" t="s">
         <v>1048</v>
       </c>
@@ -15644,7 +15668,7 @@
       </c>
       <c r="K26" s="56"/>
     </row>
-    <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A27" s="54" t="s">
         <v>1052</v>
       </c>
@@ -15677,7 +15701,7 @@
       </c>
       <c r="K27" s="56"/>
     </row>
-    <row r="28" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="57"/>
       <c r="B28" s="55" t="s">
         <v>1056</v>
@@ -15694,7 +15718,7 @@
       <c r="J28" s="56"/>
       <c r="K28" s="56"/>
     </row>
-    <row r="29" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57"/>
       <c r="B29" s="55" t="s">
         <v>1058</v>
@@ -15711,7 +15735,7 @@
       <c r="J29" s="56"/>
       <c r="K29" s="56"/>
     </row>
-    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="54" t="s">
         <v>1060</v>
       </c>
@@ -15744,7 +15768,7 @@
       </c>
       <c r="K30" s="56"/>
     </row>
-    <row r="31" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="57"/>
       <c r="B31" s="55" t="s">
         <v>1065</v>
@@ -15761,7 +15785,7 @@
       <c r="J31" s="56"/>
       <c r="K31" s="56"/>
     </row>
-    <row r="32" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="57"/>
       <c r="B32" s="55" t="s">
         <v>1067</v>
@@ -15778,7 +15802,7 @@
       <c r="J32" s="56"/>
       <c r="K32" s="56"/>
     </row>
-    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
         <v>1069</v>
       </c>
@@ -15811,7 +15835,7 @@
       </c>
       <c r="K33" s="56"/>
     </row>
-    <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="54" t="s">
         <v>1074</v>
       </c>
@@ -15844,7 +15868,7 @@
       </c>
       <c r="K34" s="56"/>
     </row>
-    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A35" s="54" t="s">
         <v>1078</v>
       </c>
@@ -15877,7 +15901,7 @@
       </c>
       <c r="K35" s="56"/>
     </row>
-    <row r="36" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
         <v>1082</v>
       </c>
@@ -15896,7 +15920,7 @@
       <c r="J36" s="56"/>
       <c r="K36" s="56"/>
     </row>
-    <row r="37" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
         <v>1084</v>
       </c>
@@ -15941,16 +15965,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="29.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" customWidth="1"/>
+    <col min="5" max="5" width="29.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="72" t="s">
         <v>922</v>
       </c>
@@ -15967,7 +15991,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
         <v>1090</v>
       </c>
@@ -15976,7 +16000,7 @@
       <c r="D2" s="82"/>
       <c r="E2" s="82"/>
     </row>
-    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55">
         <v>2114</v>
       </c>
@@ -15993,7 +16017,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
         <v>1095</v>
       </c>
@@ -16010,7 +16034,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>1097</v>
       </c>
@@ -16021,7 +16045,7 @@
       <c r="D5" s="58"/>
       <c r="E5" s="58"/>
     </row>
-    <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="55">
         <v>10273</v>
       </c>
@@ -16038,7 +16062,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
         <v>1101</v>
       </c>
@@ -16055,7 +16079,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
         <v>1103</v>
       </c>
@@ -16066,7 +16090,7 @@
       <c r="D8" s="58"/>
       <c r="E8" s="58"/>
     </row>
-    <row r="9" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
         <v>1105</v>
       </c>
@@ -16083,7 +16107,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
         <v>1108</v>
       </c>
@@ -16100,7 +16124,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="55">
         <v>40960</v>
       </c>
@@ -16117,7 +16141,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="55">
         <v>51266</v>
       </c>
@@ -16134,7 +16158,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="55" t="s">
         <v>1115</v>
       </c>
@@ -16166,14 +16190,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1117</v>
       </c>
@@ -16187,7 +16211,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="73">
         <v>32768</v>
       </c>
@@ -16202,7 +16226,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="73">
         <f t="shared" ref="A3:A61" si="1">SUM(A2, 1)</f>
         <v>32769</v>
@@ -16216,7 +16240,7 @@
       </c>
       <c r="D3" s="74"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="73">
         <f t="shared" si="1"/>
         <v>32770</v>
@@ -16230,7 +16254,7 @@
       </c>
       <c r="D4" s="74"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="73">
         <f t="shared" si="1"/>
         <v>32771</v>
@@ -16246,7 +16270,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="73">
         <f t="shared" si="1"/>
         <v>32772</v>
@@ -16260,7 +16284,7 @@
       </c>
       <c r="D6" s="74"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="73">
         <f t="shared" si="1"/>
         <v>32773</v>
@@ -16272,7 +16296,7 @@
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="73">
         <f t="shared" si="1"/>
         <v>32774</v>
@@ -16284,7 +16308,7 @@
       <c r="C8" s="74"/>
       <c r="D8" s="74"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="73">
         <f t="shared" si="1"/>
         <v>32775</v>
@@ -16296,7 +16320,7 @@
       <c r="C9" s="74"/>
       <c r="D9" s="74"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="73">
         <f t="shared" si="1"/>
         <v>32776</v>
@@ -16308,7 +16332,7 @@
       <c r="C10" s="74"/>
       <c r="D10" s="74"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73">
         <f t="shared" si="1"/>
         <v>32777</v>
@@ -16320,7 +16344,7 @@
       <c r="C11" s="74"/>
       <c r="D11" s="74"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="73">
         <f t="shared" si="1"/>
         <v>32778</v>
@@ -16332,7 +16356,7 @@
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="73">
         <f t="shared" si="1"/>
         <v>32779</v>
@@ -16344,7 +16368,7 @@
       <c r="C13" s="74"/>
       <c r="D13" s="74"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="73">
         <f t="shared" si="1"/>
         <v>32780</v>
@@ -16356,7 +16380,7 @@
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="73">
         <f t="shared" si="1"/>
         <v>32781</v>
@@ -16372,7 +16396,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73">
         <f t="shared" si="1"/>
         <v>32782</v>
@@ -16386,7 +16410,7 @@
       </c>
       <c r="D16" s="74"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="73">
         <f t="shared" si="1"/>
         <v>32783</v>
@@ -16402,7 +16426,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="73">
         <f t="shared" si="1"/>
         <v>32784</v>
@@ -16416,7 +16440,7 @@
       </c>
       <c r="D18" s="74"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="73">
         <f t="shared" si="1"/>
         <v>32785</v>
@@ -16430,7 +16454,7 @@
       </c>
       <c r="D19" s="74"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="73">
         <f t="shared" si="1"/>
         <v>32786</v>
@@ -16442,7 +16466,7 @@
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="73">
         <f t="shared" si="1"/>
         <v>32787</v>
@@ -16456,7 +16480,7 @@
       </c>
       <c r="D21" s="74"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="73">
         <f t="shared" si="1"/>
         <v>32788</v>
@@ -16470,7 +16494,7 @@
       </c>
       <c r="D22" s="74"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="73">
         <f t="shared" si="1"/>
         <v>32789</v>
@@ -16484,7 +16508,7 @@
       </c>
       <c r="D23" s="74"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="73">
         <f t="shared" si="1"/>
         <v>32790</v>
@@ -16498,7 +16522,7 @@
       </c>
       <c r="D24" s="74"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="73">
         <f t="shared" si="1"/>
         <v>32791</v>
@@ -16514,7 +16538,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="73">
         <f t="shared" si="1"/>
         <v>32792</v>
@@ -16530,7 +16554,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="73">
         <f t="shared" si="1"/>
         <v>32793</v>
@@ -16546,7 +16570,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="73">
         <f t="shared" si="1"/>
         <v>32794</v>
@@ -16562,7 +16586,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="73">
         <f t="shared" si="1"/>
         <v>32795</v>
@@ -16578,7 +16602,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="73">
         <f t="shared" si="1"/>
         <v>32796</v>
@@ -16594,7 +16618,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="73">
         <f t="shared" si="1"/>
         <v>32797</v>
@@ -16606,7 +16630,7 @@
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="73">
         <f t="shared" si="1"/>
         <v>32798</v>
@@ -16618,7 +16642,7 @@
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="73">
         <f t="shared" si="1"/>
         <v>32799</v>
@@ -16630,7 +16654,7 @@
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
     </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="73">
         <f t="shared" si="1"/>
         <v>32800</v>
@@ -16642,7 +16666,7 @@
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>
     </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="73">
         <f t="shared" si="1"/>
         <v>32801</v>
@@ -16658,7 +16682,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="73">
         <f t="shared" si="1"/>
         <v>32802</v>
@@ -16672,7 +16696,7 @@
       </c>
       <c r="D36" s="74"/>
     </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="73">
         <f t="shared" si="1"/>
         <v>32803</v>
@@ -16688,7 +16712,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="73">
         <f t="shared" si="1"/>
         <v>32804</v>
@@ -16704,7 +16728,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="73">
         <f t="shared" si="1"/>
         <v>32805</v>
@@ -16720,7 +16744,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="73">
         <f t="shared" si="1"/>
         <v>32806</v>
@@ -16736,7 +16760,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="73">
         <f t="shared" si="1"/>
         <v>32807</v>
@@ -16748,7 +16772,7 @@
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
     </row>
-    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="73">
         <f t="shared" si="1"/>
         <v>32808</v>
@@ -16760,7 +16784,7 @@
       <c r="C42" s="74"/>
       <c r="D42" s="74"/>
     </row>
-    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="73">
         <f t="shared" si="1"/>
         <v>32809</v>
@@ -16772,7 +16796,7 @@
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
     </row>
-    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="73">
         <f t="shared" si="1"/>
         <v>32810</v>
@@ -16784,7 +16808,7 @@
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
     </row>
-    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="73">
         <f t="shared" si="1"/>
         <v>32811</v>
@@ -16796,7 +16820,7 @@
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
     </row>
-    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="73">
         <f t="shared" si="1"/>
         <v>32812</v>
@@ -16808,7 +16832,7 @@
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
     </row>
-    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="73">
         <f t="shared" si="1"/>
         <v>32813</v>
@@ -16820,7 +16844,7 @@
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
     </row>
-    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="73">
         <f t="shared" si="1"/>
         <v>32814</v>
@@ -16832,7 +16856,7 @@
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
     </row>
-    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="73">
         <f t="shared" si="1"/>
         <v>32815</v>
@@ -16844,7 +16868,7 @@
       <c r="C49" s="74"/>
       <c r="D49" s="74"/>
     </row>
-    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="73">
         <f t="shared" si="1"/>
         <v>32816</v>
@@ -16856,7 +16880,7 @@
       <c r="C50" s="74"/>
       <c r="D50" s="74"/>
     </row>
-    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="73">
         <f t="shared" si="1"/>
         <v>32817</v>
@@ -16870,7 +16894,7 @@
       </c>
       <c r="D51" s="74"/>
     </row>
-    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="73">
         <f t="shared" si="1"/>
         <v>32818</v>
@@ -16882,7 +16906,7 @@
       <c r="C52" s="74"/>
       <c r="D52" s="74"/>
     </row>
-    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="73">
         <f t="shared" si="1"/>
         <v>32819</v>
@@ -16894,7 +16918,7 @@
       <c r="C53" s="74"/>
       <c r="D53" s="74"/>
     </row>
-    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="73">
         <f t="shared" si="1"/>
         <v>32820</v>
@@ -16906,7 +16930,7 @@
       <c r="C54" s="74"/>
       <c r="D54" s="74"/>
     </row>
-    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="73">
         <f t="shared" si="1"/>
         <v>32821</v>
@@ -16918,7 +16942,7 @@
       <c r="C55" s="74"/>
       <c r="D55" s="74"/>
     </row>
-    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="73">
         <f t="shared" si="1"/>
         <v>32822</v>
@@ -16930,7 +16954,7 @@
       <c r="C56" s="74"/>
       <c r="D56" s="74"/>
     </row>
-    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="73">
         <f t="shared" si="1"/>
         <v>32823</v>
@@ -16942,7 +16966,7 @@
       <c r="C57" s="74"/>
       <c r="D57" s="74"/>
     </row>
-    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="73">
         <f t="shared" si="1"/>
         <v>32824</v>
@@ -16954,7 +16978,7 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
     </row>
-    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="73">
         <f t="shared" si="1"/>
         <v>32825</v>
@@ -16970,7 +16994,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="73">
         <f t="shared" si="1"/>
         <v>32826</v>
@@ -16982,7 +17006,7 @@
       <c r="C60" s="74"/>
       <c r="D60" s="74"/>
     </row>
-    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="73">
         <f t="shared" si="1"/>
         <v>32827</v>
@@ -17007,13 +17031,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.85546875" customWidth="1"/>
-    <col min="2" max="2" width="60.5703125" customWidth="1"/>
+    <col min="1" max="1" width="39.81640625" customWidth="1"/>
+    <col min="2" max="2" width="60.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="75" t="s">
         <v>1161</v>
       </c>
@@ -17021,13 +17045,13 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="85" t="s">
         <v>1162</v>
       </c>
       <c r="B2" s="82"/>
     </row>
-    <row r="3" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>1163</v>
       </c>
@@ -17035,7 +17059,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>329</v>
       </c>
@@ -17043,7 +17067,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>332</v>
       </c>
@@ -17051,7 +17075,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>335</v>
       </c>
@@ -17059,7 +17083,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>338</v>
       </c>
@@ -17067,7 +17091,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>341</v>
       </c>
@@ -17075,7 +17099,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>345</v>
       </c>
@@ -17083,7 +17107,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>368</v>
       </c>
@@ -17091,7 +17115,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>1170</v>
       </c>
@@ -17099,7 +17123,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>1172</v>
       </c>
@@ -17107,31 +17131,31 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="85" t="s">
         <v>1174</v>
       </c>
       <c r="B13" s="82"/>
     </row>
-    <row r="14" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="86" t="s">
         <v>1175</v>
       </c>
       <c r="B14" s="82"/>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="85" t="s">
         <v>1176</v>
       </c>
       <c r="B15" s="82"/>
     </row>
-    <row r="16" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A16" s="86" t="s">
         <v>1177</v>
       </c>
       <c r="B16" s="82"/>
     </row>
-    <row r="17" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>327</v>
       </c>
@@ -17139,7 +17163,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
         <v>1179</v>
       </c>
@@ -17147,7 +17171,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
         <v>1181</v>
       </c>
@@ -17155,7 +17179,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
         <v>1183</v>
       </c>
@@ -17163,7 +17187,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17171,7 +17195,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17179,7 +17203,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17187,7 +17211,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
         <v>1191</v>
       </c>
@@ -17195,7 +17219,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
         <v>1193</v>
       </c>
@@ -17203,7 +17227,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
         <v>1195</v>
       </c>
@@ -17211,19 +17235,19 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="85" t="s">
         <v>1197</v>
       </c>
       <c r="B27" s="82"/>
     </row>
-    <row r="28" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="86" t="s">
         <v>1198</v>
       </c>
       <c r="B28" s="82"/>
     </row>
-    <row r="29" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
         <v>1199</v>
       </c>
@@ -17231,7 +17255,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>1201</v>
       </c>
@@ -17239,7 +17263,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>1203</v>
       </c>
@@ -17247,7 +17271,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
         <v>1205</v>
       </c>
@@ -17255,13 +17279,13 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="85" t="s">
         <v>1207</v>
       </c>
       <c r="B33" s="82"/>
     </row>
-    <row r="34" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
         <v>327</v>
       </c>
@@ -17269,7 +17293,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="76" t="s">
         <v>1209</v>
       </c>
@@ -17277,7 +17301,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="76" t="s">
         <v>1179</v>
       </c>
@@ -17285,7 +17309,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
         <v>1212</v>
       </c>
@@ -17293,7 +17317,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="76" t="s">
         <v>1181</v>
       </c>
@@ -17301,7 +17325,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
         <v>1215</v>
       </c>
@@ -17309,7 +17333,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
         <v>1217</v>
       </c>
@@ -17317,7 +17341,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
         <v>1219</v>
       </c>
@@ -17325,7 +17349,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="76" t="s">
         <v>1183</v>
       </c>
@@ -17333,7 +17357,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
         <v>1222</v>
       </c>
@@ -17341,7 +17365,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="23" t="s">
         <v>1224</v>
       </c>
@@ -17349,7 +17373,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="23" t="s">
         <v>1226</v>
       </c>
@@ -17357,7 +17381,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="23" t="s">
         <v>1228</v>
       </c>
@@ -17365,7 +17389,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
         <v>1230</v>
       </c>
@@ -17373,7 +17397,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
         <v>1232</v>
       </c>
@@ -17381,7 +17405,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="23" t="s">
         <v>1234</v>
       </c>
@@ -17389,7 +17413,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17397,7 +17421,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17405,7 +17429,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17413,13 +17437,13 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A53" s="85" t="s">
         <v>1239</v>
       </c>
       <c r="B53" s="82"/>
     </row>
-    <row r="54" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
         <v>327</v>
       </c>
@@ -17427,7 +17451,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="76" t="s">
         <v>1179</v>
       </c>
@@ -17435,7 +17459,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="76" t="s">
         <v>1181</v>
       </c>
@@ -17443,7 +17467,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
         <v>1217</v>
       </c>
@@ -17451,7 +17475,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="76" t="s">
         <v>1183</v>
       </c>
@@ -17459,7 +17483,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
         <v>1224</v>
       </c>
@@ -17467,7 +17491,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="23" t="s">
         <v>1228</v>
       </c>
@@ -17475,7 +17499,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
         <v>1232</v>
       </c>
@@ -17483,7 +17507,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="76" t="s">
         <v>1185</v>
       </c>
@@ -17491,7 +17515,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
         <v>1249</v>
       </c>
@@ -17499,7 +17523,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="23" t="s">
         <v>1251</v>
       </c>
@@ -17507,7 +17531,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
         <v>1253</v>
       </c>
@@ -17515,7 +17539,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
         <v>1255</v>
       </c>
@@ -17523,7 +17547,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="23" t="s">
         <v>1257</v>
       </c>
@@ -17531,7 +17555,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
         <v>1259</v>
       </c>
@@ -17539,7 +17563,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
         <v>1261</v>
       </c>
@@ -17547,13 +17571,13 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A70" s="85" t="s">
         <v>1263</v>
       </c>
       <c r="B70" s="82"/>
     </row>
-    <row r="71" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
         <v>327</v>
       </c>
@@ -17561,7 +17585,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A72" s="23" t="s">
         <v>1181</v>
       </c>
@@ -17569,7 +17593,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="23" t="s">
         <v>1183</v>
       </c>
@@ -17577,7 +17601,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17585,7 +17609,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17593,13 +17617,13 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A76" s="85" t="s">
         <v>1269</v>
       </c>
       <c r="B76" s="82"/>
     </row>
-    <row r="77" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="23" t="s">
         <v>327</v>
       </c>
@@ -17607,7 +17631,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17615,7 +17639,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17623,7 +17647,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>1191</v>
       </c>

--- a/Tekken 8 Moveset Editing Data.xlsx
+++ b/Tekken 8 Moveset Editing Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cSles\Desktop\Modding\Tekken8Movesets_OWN_PROJECTS\extracted_chars\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cs\Documents\GitHub\Tekken8Movesets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CEE8F6-4CBF-4E42-B52F-2CD2AEC0CF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFB5831-6F2D-4B30-8E0D-7E3525E32610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -6553,15 +6553,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D257"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="51.1796875" customWidth="1"/>
-    <col min="4" max="4" width="68.81640625" customWidth="1"/>
+    <col min="3" max="3" width="51.140625" customWidth="1"/>
+    <col min="4" max="4" width="68.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1100</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>0</v>
       </c>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D19" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D20" s="8"/>
     </row>
-    <row r="21" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>18</v>
       </c>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>23</v>
       </c>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>24</v>
       </c>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>25</v>
       </c>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>26</v>
       </c>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>27</v>
       </c>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>28</v>
       </c>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>29</v>
       </c>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>30</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>31</v>
       </c>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>32</v>
       </c>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>33</v>
       </c>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>34</v>
       </c>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>35</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>36</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>43</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>44</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>47</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>48</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>49</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>50</v>
       </c>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>51</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>61</v>
       </c>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>62</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>63</v>
       </c>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>64</v>
       </c>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D46" s="8"/>
     </row>
-    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>65</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>66</v>
       </c>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="D48" s="8"/>
     </row>
-    <row r="49" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>67</v>
       </c>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D49" s="8"/>
     </row>
-    <row r="50" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>68</v>
       </c>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>69</v>
       </c>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>70</v>
       </c>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>71</v>
       </c>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>72</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>73</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>76</v>
       </c>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>77</v>
       </c>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="D57" s="8"/>
     </row>
-    <row r="58" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>87</v>
       </c>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>92</v>
       </c>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>93</v>
       </c>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>94</v>
       </c>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>95</v>
       </c>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D62" s="8"/>
     </row>
-    <row r="63" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>96</v>
       </c>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>97</v>
       </c>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>98</v>
       </c>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>99</v>
       </c>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>100</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>101</v>
       </c>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D68" s="8"/>
     </row>
-    <row r="69" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>102</v>
       </c>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D69" s="8"/>
     </row>
-    <row r="70" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>103</v>
       </c>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>104</v>
       </c>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>105</v>
       </c>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>106</v>
       </c>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>107</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>108</v>
       </c>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D75" s="8"/>
     </row>
-    <row r="76" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>109</v>
       </c>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D76" s="8"/>
     </row>
-    <row r="77" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>110</v>
       </c>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>111</v>
       </c>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>112</v>
       </c>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>126</v>
       </c>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>127</v>
       </c>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="D81" s="8"/>
     </row>
-    <row r="82" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>128</v>
       </c>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D82" s="8"/>
     </row>
-    <row r="83" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>130</v>
       </c>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>131</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>132</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>133</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>134</v>
       </c>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D87" s="8"/>
     </row>
-    <row r="88" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>135</v>
       </c>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="D88" s="8"/>
     </row>
-    <row r="89" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>137</v>
       </c>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D89" s="8"/>
     </row>
-    <row r="90" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>138</v>
       </c>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="D90" s="12"/>
     </row>
-    <row r="91" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>139</v>
       </c>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D91" s="8"/>
     </row>
-    <row r="92" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>140</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>141</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>142</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>143</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>144</v>
       </c>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D96" s="8"/>
     </row>
-    <row r="97" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>145</v>
       </c>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D97" s="8"/>
     </row>
-    <row r="98" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>146</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>147</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>148</v>
       </c>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D100" s="8"/>
     </row>
-    <row r="101" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>149</v>
       </c>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D101" s="8"/>
     </row>
-    <row r="102" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>150</v>
       </c>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D102" s="8"/>
     </row>
-    <row r="103" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>151</v>
       </c>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D103" s="8"/>
     </row>
-    <row r="104" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>152</v>
       </c>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="D104" s="9"/>
     </row>
-    <row r="105" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>153</v>
       </c>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D105" s="9"/>
     </row>
-    <row r="106" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>157</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>158</v>
       </c>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D107" s="8"/>
     </row>
-    <row r="108" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>159</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>168</v>
       </c>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="D109" s="9"/>
     </row>
-    <row r="110" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>184</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>192</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>219</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>220</v>
       </c>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D113" s="8"/>
     </row>
-    <row r="114" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>221</v>
       </c>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D114" s="8"/>
     </row>
-    <row r="115" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>222</v>
       </c>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D115" s="8"/>
     </row>
-    <row r="116" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>223</v>
       </c>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D116" s="8"/>
     </row>
-    <row r="117" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>224</v>
       </c>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>225</v>
       </c>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>226</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>227</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>228</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>229</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>236</v>
       </c>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="D123" s="12"/>
     </row>
-    <row r="124" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A124" s="13">
         <v>238</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>259</v>
       </c>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D125" s="12"/>
     </row>
-    <row r="126" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>274</v>
       </c>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D126" s="12"/>
     </row>
-    <row r="127" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>276</v>
       </c>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D127" s="12"/>
     </row>
-    <row r="128" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>280</v>
       </c>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D128" s="12"/>
     </row>
-    <row r="129" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>281</v>
       </c>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="D129" s="12"/>
     </row>
-    <row r="130" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>282</v>
       </c>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D130" s="12"/>
     </row>
-    <row r="131" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>283</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D131" s="12"/>
     </row>
-    <row r="132" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>288</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>297</v>
       </c>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D133" s="12"/>
     </row>
-    <row r="134" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>312</v>
       </c>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D134" s="12"/>
     </row>
-    <row r="135" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>314</v>
       </c>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="D135" s="12"/>
     </row>
-    <row r="136" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>318</v>
       </c>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="D136" s="12"/>
     </row>
-    <row r="137" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>319</v>
       </c>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D137" s="12"/>
     </row>
-    <row r="138" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>320</v>
       </c>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D138" s="12"/>
     </row>
-    <row r="139" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>321</v>
       </c>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D139" s="12"/>
     </row>
-    <row r="140" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>326</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>335</v>
       </c>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D141" s="12"/>
     </row>
-    <row r="142" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>350</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>352</v>
       </c>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D143" s="12"/>
     </row>
-    <row r="144" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>356</v>
       </c>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="D144" s="12"/>
     </row>
-    <row r="145" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>358</v>
       </c>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D145" s="12"/>
     </row>
-    <row r="146" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>359</v>
       </c>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D146" s="12"/>
     </row>
-    <row r="147" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>360</v>
       </c>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="D147" s="12"/>
     </row>
-    <row r="148" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>365</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>442</v>
       </c>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D149" s="12"/>
     </row>
-    <row r="150" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>454</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="13">
         <v>466</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>473</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="14">
         <v>490</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="14">
         <v>498</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A155" s="16">
         <v>499</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="16">
         <v>500</v>
       </c>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D156" s="19"/>
     </row>
-    <row r="157" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="16">
         <v>501</v>
       </c>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="D157" s="19"/>
     </row>
-    <row r="158" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="16">
         <v>502</v>
       </c>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D158" s="19"/>
     </row>
-    <row r="159" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="16">
         <v>503</v>
       </c>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="D159" s="19"/>
     </row>
-    <row r="160" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="16">
         <v>504</v>
       </c>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4" ht="38" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A161" s="16">
         <v>505</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="16">
         <v>506</v>
       </c>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D162" s="19"/>
     </row>
-    <row r="163" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="14">
         <v>640</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="14">
         <v>641</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="14">
         <v>642</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>648</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>649</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>652</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>653</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>654</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>655</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>656</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>657</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>658</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>659</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>660</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="38" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>661</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="13">
         <v>662</v>
       </c>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D178" s="13"/>
     </row>
-    <row r="179" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>664</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>666</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>667</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>668</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>672</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="12">
         <v>687</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>689</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="12">
         <v>690</v>
       </c>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D186" s="12"/>
     </row>
-    <row r="187" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>691</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="12">
         <v>692</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>693</v>
       </c>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="D189" s="12"/>
     </row>
-    <row r="190" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="12">
         <v>694</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>695</v>
       </c>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D191" s="12"/>
     </row>
-    <row r="192" spans="1:4" ht="25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A192" s="12">
         <v>696</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>716</v>
       </c>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="D193" s="12"/>
     </row>
-    <row r="194" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="12">
         <v>717</v>
       </c>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D194" s="12"/>
     </row>
-    <row r="195" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>718</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="12">
         <v>723</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="12">
         <v>724</v>
       </c>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D197" s="12"/>
     </row>
-    <row r="198" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="12">
         <v>750</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="12">
         <v>751</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="13">
         <v>755</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="12">
         <v>758</v>
       </c>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D201" s="12"/>
     </row>
-    <row r="202" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="13">
         <v>766</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="13">
         <v>767</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="38" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A204" s="12">
         <v>777</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="12">
         <v>778</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A206" s="13">
         <v>783</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A207" s="13">
         <v>784</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A208" s="13">
         <v>785</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="12">
         <v>790</v>
       </c>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="D209" s="12"/>
     </row>
-    <row r="210" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="12">
         <v>791</v>
       </c>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D210" s="12"/>
     </row>
-    <row r="211" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="12">
         <v>792</v>
       </c>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="D211" s="12"/>
     </row>
-    <row r="212" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="12">
         <v>793</v>
       </c>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D212" s="12"/>
     </row>
-    <row r="213" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="12">
         <v>794</v>
       </c>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D213" s="12"/>
     </row>
-    <row r="214" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="12">
         <v>795</v>
       </c>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D214" s="12"/>
     </row>
-    <row r="215" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A215" s="12">
         <v>796</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="13">
         <v>799</v>
       </c>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="D216" s="13"/>
     </row>
-    <row r="217" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="13">
         <v>800</v>
       </c>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="D217" s="13"/>
     </row>
-    <row r="218" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="12">
         <v>801</v>
       </c>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D218" s="12"/>
     </row>
-    <row r="219" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="12">
         <v>802</v>
       </c>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D219" s="12"/>
     </row>
-    <row r="220" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="12">
         <v>803</v>
       </c>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D220" s="12"/>
     </row>
-    <row r="221" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A221" s="13">
         <v>804</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="12">
         <v>806</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="26" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A223" s="13">
         <v>1016</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="12">
         <v>1028</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="23">
         <v>1032</v>
       </c>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="D225" s="21"/>
     </row>
-    <row r="226" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="23">
         <v>1033</v>
       </c>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="D226" s="21"/>
     </row>
-    <row r="227" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="12">
         <v>1034</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="12">
         <v>1035</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="23">
         <v>1036</v>
       </c>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D229" s="12"/>
     </row>
-    <row r="230" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="23">
         <v>1038</v>
       </c>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="D230" s="12"/>
     </row>
-    <row r="231" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="23">
         <v>1039</v>
       </c>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D231" s="12"/>
     </row>
-    <row r="232" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="12">
         <v>1040</v>
       </c>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D232" s="12"/>
     </row>
-    <row r="233" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="12">
         <v>1041</v>
       </c>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="D233" s="12"/>
     </row>
-    <row r="234" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="23">
         <v>1042</v>
       </c>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D234" s="12"/>
     </row>
-    <row r="235" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="12">
         <v>1049</v>
       </c>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D235" s="12"/>
     </row>
-    <row r="236" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="23">
         <v>1061</v>
       </c>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="D236" s="25"/>
     </row>
-    <row r="237" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="23">
         <v>1062</v>
       </c>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="D237" s="25"/>
     </row>
-    <row r="238" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="12">
         <v>1063</v>
       </c>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="D238" s="25"/>
     </row>
-    <row r="239" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="12">
         <v>1064</v>
       </c>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="D239" s="25"/>
     </row>
-    <row r="240" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="23">
         <v>1065</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="23">
         <v>1067</v>
       </c>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D241" s="26"/>
     </row>
-    <row r="242" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="23">
         <v>1068</v>
       </c>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D242" s="26"/>
     </row>
-    <row r="243" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="12">
         <v>1069</v>
       </c>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D243" s="26"/>
     </row>
-    <row r="244" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="12">
         <v>1070</v>
       </c>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D244" s="26"/>
     </row>
-    <row r="245" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="23">
         <v>1071</v>
       </c>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="D245" s="26"/>
     </row>
-    <row r="246" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="23">
         <v>1078</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="23">
         <v>1079</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D247" s="25"/>
     </row>
-    <row r="248" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="12">
         <v>1080</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="12">
         <v>1081</v>
       </c>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="D249" s="26"/>
     </row>
-    <row r="250" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="23">
         <v>1082</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="23">
         <v>1083</v>
       </c>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="D251" s="25"/>
     </row>
-    <row r="252" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="12">
         <v>1084</v>
       </c>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D252" s="25"/>
     </row>
-    <row r="253" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="12">
         <v>1085</v>
       </c>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D253" s="25"/>
     </row>
-    <row r="254" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="23">
         <v>1090</v>
       </c>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="D254" s="25"/>
     </row>
-    <row r="255" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="23">
         <v>1091</v>
       </c>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="D255" s="25"/>
     </row>
-    <row r="256" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="23">
         <v>1092</v>
       </c>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="D256" s="25"/>
     </row>
-    <row r="257" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="23">
         <v>1093</v>
       </c>
@@ -9851,16 +9851,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E213"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" customWidth="1"/>
-    <col min="3" max="3" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.453125" customWidth="1"/>
-    <col min="5" max="5" width="34.1796875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>322</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
         <v>327</v>
       </c>
@@ -9890,7 +9890,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
         <v>329</v>
       </c>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="E3" s="29"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
         <v>332</v>
       </c>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="E4" s="29"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="28" t="s">
         <v>335</v>
       </c>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="E5" s="29"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>338</v>
       </c>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="E6" s="29"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="28" t="s">
         <v>341</v>
       </c>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="E7" s="29"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="28" t="s">
         <v>345</v>
       </c>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="E8" s="29"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="28" t="s">
         <v>347</v>
       </c>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="E9" s="29"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="28" t="s">
         <v>349</v>
       </c>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="E10" s="29"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="28" t="s">
         <v>351</v>
       </c>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="E11" s="29"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28" t="s">
         <v>353</v>
       </c>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="E12" s="29"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28" t="s">
         <v>354</v>
       </c>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E13" s="29"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="28" t="s">
         <v>357</v>
       </c>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="E14" s="29"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="30" t="s">
         <v>360</v>
       </c>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="E15" s="31"/>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30" t="s">
         <v>363</v>
       </c>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E16" s="31"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="30" t="s">
         <v>366</v>
       </c>
@@ -10113,7 +10113,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="31"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
         <v>368</v>
       </c>
@@ -10126,7 +10126,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="31"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="30" t="s">
         <v>370</v>
       </c>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="E19" s="31"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="30" t="s">
         <v>373</v>
       </c>
@@ -10154,7 +10154,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="31"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="30" t="s">
         <v>375</v>
       </c>
@@ -10167,7 +10167,7 @@
       <c r="D21" s="14"/>
       <c r="E21" s="31"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="30" t="s">
         <v>377</v>
       </c>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="E22" s="31"/>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="30" t="s">
         <v>380</v>
       </c>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="E23" s="35"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
         <v>382</v>
       </c>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="E24" s="31"/>
     </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="28" t="s">
         <v>386</v>
       </c>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="28" t="s">
         <v>389</v>
       </c>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E26" s="29"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="28" t="s">
         <v>392</v>
       </c>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="E27" s="29"/>
     </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="28" t="s">
         <v>395</v>
       </c>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="E28" s="29"/>
     </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="28" t="s">
         <v>398</v>
       </c>
@@ -10285,7 +10285,7 @@
       <c r="D29" s="6"/>
       <c r="E29" s="29"/>
     </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="28" t="s">
         <v>400</v>
       </c>
@@ -10298,7 +10298,7 @@
       <c r="D30" s="6"/>
       <c r="E30" s="29"/>
     </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="28" t="s">
         <v>402</v>
       </c>
@@ -10311,7 +10311,7 @@
       <c r="D31" s="6"/>
       <c r="E31" s="29"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="28" t="s">
         <v>404</v>
       </c>
@@ -10324,7 +10324,7 @@
       <c r="D32" s="6"/>
       <c r="E32" s="29"/>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="28" t="s">
         <v>406</v>
       </c>
@@ -10337,7 +10337,7 @@
       <c r="D33" s="6"/>
       <c r="E33" s="29"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="28" t="s">
         <v>408</v>
       </c>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="E34" s="29"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="28" t="s">
         <v>412</v>
       </c>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E35" s="29"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="28" t="s">
         <v>415</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="28" t="s">
         <v>420</v>
       </c>
@@ -10397,7 +10397,7 @@
       <c r="D37" s="6"/>
       <c r="E37" s="29"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="28" t="s">
         <v>422</v>
       </c>
@@ -10410,7 +10410,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A39" s="28" t="s">
         <v>424</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="28" t="s">
         <v>428</v>
       </c>
@@ -10440,7 +10440,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="29"/>
     </row>
-    <row r="41" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="28" t="s">
         <v>430</v>
       </c>
@@ -10453,7 +10453,7 @@
       <c r="D41" s="6"/>
       <c r="E41" s="29"/>
     </row>
-    <row r="42" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A42" s="28" t="s">
         <v>432</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="28" t="s">
         <v>434</v>
       </c>
@@ -10483,7 +10483,7 @@
       <c r="D43" s="6"/>
       <c r="E43" s="29"/>
     </row>
-    <row r="44" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="28" t="s">
         <v>436</v>
       </c>
@@ -10496,7 +10496,7 @@
       <c r="D44" s="6"/>
       <c r="E44" s="29"/>
     </row>
-    <row r="45" spans="1:5" ht="38.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="28" t="s">
         <v>438</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="28" t="s">
         <v>441</v>
       </c>
@@ -10526,7 +10526,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="29"/>
     </row>
-    <row r="47" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="28" t="s">
         <v>443</v>
       </c>
@@ -10539,7 +10539,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="29"/>
     </row>
-    <row r="48" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A48" s="28" t="s">
         <v>445</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="28" t="s">
         <v>449</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="28" t="s">
         <v>452</v>
       </c>
@@ -10586,7 +10586,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="28" t="s">
         <v>454</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="28" t="s">
         <v>457</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A53" s="28" t="s">
         <v>460</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="28" t="s">
         <v>462</v>
       </c>
@@ -10650,7 +10650,7 @@
       <c r="D54" s="6"/>
       <c r="E54" s="29"/>
     </row>
-    <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="28" t="s">
         <v>464</v>
       </c>
@@ -10663,7 +10663,7 @@
       <c r="D55" s="6"/>
       <c r="E55" s="29"/>
     </row>
-    <row r="56" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A56" s="28" t="s">
         <v>466</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="28" t="s">
         <v>469</v>
       </c>
@@ -10693,7 +10693,7 @@
       <c r="D57" s="6"/>
       <c r="E57" s="29"/>
     </row>
-    <row r="58" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="28" t="s">
         <v>471</v>
       </c>
@@ -10706,7 +10706,7 @@
       <c r="D58" s="6"/>
       <c r="E58" s="29"/>
     </row>
-    <row r="59" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A59" s="28" t="s">
         <v>473</v>
       </c>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="E59" s="8"/>
     </row>
-    <row r="60" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A60" s="28" t="s">
         <v>475</v>
       </c>
@@ -10734,7 +10734,7 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row r="61" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A61" s="28" t="s">
         <v>477</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A62" s="28" t="s">
         <v>479</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A63" s="28" t="s">
         <v>481</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A64" s="28" t="s">
         <v>483</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="28" t="s">
         <v>487</v>
       </c>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E65" s="29"/>
     </row>
-    <row r="66" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="28" t="s">
         <v>490</v>
       </c>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="E66" s="29"/>
     </row>
-    <row r="67" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A67" s="28" t="s">
         <v>492</v>
       </c>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="E67" s="29"/>
     </row>
-    <row r="68" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A68" s="28" t="s">
         <v>494</v>
       </c>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="E68" s="29"/>
     </row>
-    <row r="69" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A69" s="28" t="s">
         <v>496</v>
       </c>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E69" s="29"/>
     </row>
-    <row r="70" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A70" s="28" t="s">
         <v>498</v>
       </c>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="E70" s="36"/>
     </row>
-    <row r="71" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="28" t="s">
         <v>502</v>
       </c>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="E71" s="29"/>
     </row>
-    <row r="72" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="28" t="s">
         <v>506</v>
       </c>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E72" s="29"/>
     </row>
-    <row r="73" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="28" t="s">
         <v>510</v>
       </c>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E73" s="29"/>
     </row>
-    <row r="74" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A74" s="28" t="s">
         <v>513</v>
       </c>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="E74" s="36"/>
     </row>
-    <row r="75" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A75" s="28" t="s">
         <v>517</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="28" t="s">
         <v>1283</v>
       </c>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E76" s="29"/>
     </row>
-    <row r="77" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="30" t="s">
         <v>521</v>
       </c>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="E77" s="31"/>
     </row>
-    <row r="78" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="30" t="s">
         <v>524</v>
       </c>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="E78" s="31"/>
     </row>
-    <row r="79" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="30" t="s">
         <v>527</v>
       </c>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="E79" s="31"/>
     </row>
-    <row r="80" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="30" t="s">
         <v>530</v>
       </c>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E80" s="31"/>
     </row>
-    <row r="81" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="30" t="s">
         <v>533</v>
       </c>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="E81" s="31"/>
     </row>
-    <row r="82" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
         <v>536</v>
       </c>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="E82" s="31"/>
     </row>
-    <row r="83" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="28" t="s">
         <v>540</v>
       </c>
@@ -11085,7 +11085,7 @@
       <c r="D83" s="6"/>
       <c r="E83" s="29"/>
     </row>
-    <row r="84" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="28" t="s">
         <v>542</v>
       </c>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E84" s="29"/>
     </row>
-    <row r="85" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="28" t="s">
         <v>545</v>
       </c>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="E85" s="29"/>
     </row>
-    <row r="86" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="28" t="s">
         <v>548</v>
       </c>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="E86" s="29"/>
     </row>
-    <row r="87" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A87" s="28" t="s">
         <v>551</v>
       </c>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="E87" s="29"/>
     </row>
-    <row r="88" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A88" s="28" t="s">
         <v>554</v>
       </c>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E88" s="29"/>
     </row>
-    <row r="89" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="28" t="s">
         <v>557</v>
       </c>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A90" s="28" t="s">
         <v>560</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="28" t="s">
         <v>565</v>
       </c>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="E91" s="8"/>
     </row>
-    <row r="92" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="28" t="s">
         <v>568</v>
       </c>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="E92" s="8"/>
     </row>
-    <row r="93" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="28" t="s">
         <v>571</v>
       </c>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="28" t="s">
         <v>574</v>
       </c>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="E94" s="8"/>
     </row>
-    <row r="95" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="28" t="s">
         <v>577</v>
       </c>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="E95" s="8"/>
     </row>
-    <row r="96" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="28" t="s">
         <v>580</v>
       </c>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="E96" s="8"/>
     </row>
-    <row r="97" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="28" t="s">
         <v>583</v>
       </c>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="E97" s="8"/>
     </row>
-    <row r="98" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="28" t="s">
         <v>587</v>
       </c>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="E98" s="8"/>
     </row>
-    <row r="99" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="28" t="s">
         <v>589</v>
       </c>
@@ -11317,7 +11317,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="28" t="s">
         <v>594</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="28" t="s">
         <v>597</v>
       </c>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="E101" s="8"/>
     </row>
-    <row r="102" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="28" t="s">
         <v>600</v>
       </c>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="E102" s="8"/>
     </row>
-    <row r="103" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="28" t="s">
         <v>603</v>
       </c>
@@ -11377,7 +11377,7 @@
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
     </row>
-    <row r="104" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A104" s="28" t="s">
         <v>605</v>
       </c>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E104" s="8"/>
     </row>
-    <row r="105" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="28" t="s">
         <v>608</v>
       </c>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="E105" s="31"/>
     </row>
-    <row r="106" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A106" s="78" t="s">
         <v>1274</v>
       </c>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="E106" s="31"/>
     </row>
-    <row r="107" spans="1:5" ht="50.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A107" s="28" t="s">
         <v>611</v>
       </c>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E107" s="31"/>
     </row>
-    <row r="108" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A108" s="28" t="s">
         <v>614</v>
       </c>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="E108" s="31"/>
     </row>
-    <row r="109" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A109" s="28" t="s">
         <v>617</v>
       </c>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="E109" s="31"/>
     </row>
-    <row r="110" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="28" t="s">
         <v>620</v>
       </c>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="E110" s="31"/>
     </row>
-    <row r="111" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="28" t="s">
         <v>624</v>
       </c>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="E111" s="31"/>
     </row>
-    <row r="112" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="28" t="s">
         <v>627</v>
       </c>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="E112" s="31"/>
     </row>
-    <row r="113" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="28" t="s">
         <v>630</v>
       </c>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="E113" s="31"/>
     </row>
-    <row r="114" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="28" t="s">
         <v>633</v>
       </c>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="E114" s="31"/>
     </row>
-    <row r="115" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="28" t="s">
         <v>636</v>
       </c>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="E115" s="31"/>
     </row>
-    <row r="116" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="28" t="s">
         <v>639</v>
       </c>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="E116" s="31"/>
     </row>
-    <row r="117" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A117" s="28" t="s">
         <v>642</v>
       </c>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="E117" s="31"/>
     </row>
-    <row r="118" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="28" t="s">
         <v>645</v>
       </c>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="E118" s="31"/>
     </row>
-    <row r="119" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="28" t="s">
         <v>648</v>
       </c>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="E119" s="31"/>
     </row>
-    <row r="120" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A120" s="28" t="s">
         <v>651</v>
       </c>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="E120" s="31"/>
     </row>
-    <row r="121" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A121" s="28" t="s">
         <v>654</v>
       </c>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="E121" s="31"/>
     </row>
-    <row r="122" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A122" s="28" t="s">
         <v>656</v>
       </c>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="E122" s="31"/>
     </row>
-    <row r="123" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="28" t="s">
         <v>659</v>
       </c>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="E123" s="31"/>
     </row>
-    <row r="124" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A124" s="28" t="s">
         <v>662</v>
       </c>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="E124" s="31"/>
     </row>
-    <row r="125" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="28" t="s">
         <v>665</v>
       </c>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="E125" s="37"/>
     </row>
-    <row r="126" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="30" t="s">
         <v>669</v>
       </c>
@@ -11720,7 +11720,7 @@
       <c r="D126" s="32"/>
       <c r="E126" s="38"/>
     </row>
-    <row r="127" spans="1:5" ht="38" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A127" s="30" t="s">
         <v>671</v>
       </c>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="E127" s="37"/>
     </row>
-    <row r="128" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A128" s="30" t="s">
         <v>675</v>
       </c>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="E128" s="37"/>
     </row>
-    <row r="129" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A129" s="30" t="s">
         <v>678</v>
       </c>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="E129" s="31"/>
     </row>
-    <row r="130" spans="1:5" ht="38" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A130" s="28" t="s">
         <v>681</v>
       </c>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="E130" s="31"/>
     </row>
-    <row r="131" spans="1:5" ht="75.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A131" s="28" t="s">
         <v>684</v>
       </c>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E131" s="31"/>
     </row>
-    <row r="132" spans="1:5" ht="38" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A132" s="28" t="s">
         <v>688</v>
       </c>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E132" s="31"/>
     </row>
-    <row r="133" spans="1:5" ht="50.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A133" s="28" t="s">
         <v>1276</v>
       </c>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="E133" s="31"/>
     </row>
-    <row r="134" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A134" s="28" t="s">
         <v>690</v>
       </c>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="E134" s="31"/>
     </row>
-    <row r="135" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A135" s="28" t="s">
         <v>694</v>
       </c>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E135" s="31"/>
     </row>
-    <row r="136" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="28" t="s">
         <v>697</v>
       </c>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E136" s="31"/>
     </row>
-    <row r="137" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A137" s="28" t="s">
         <v>700</v>
       </c>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="E137" s="31"/>
     </row>
-    <row r="138" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A138" s="28" t="s">
         <v>704</v>
       </c>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="E138" s="37"/>
     </row>
-    <row r="139" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A139" s="28" t="s">
         <v>707</v>
       </c>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="E139" s="31"/>
     </row>
-    <row r="140" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A140" s="28" t="s">
         <v>710</v>
       </c>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="E140" s="31"/>
     </row>
-    <row r="141" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="28" t="s">
         <v>713</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="78" t="s">
         <v>1280</v>
       </c>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="E142" s="31"/>
     </row>
-    <row r="143" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A143" s="28" t="s">
         <v>717</v>
       </c>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="E143" s="31"/>
     </row>
-    <row r="144" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A144" s="28" t="s">
         <v>720</v>
       </c>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="E144" s="31"/>
     </row>
-    <row r="145" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A145" s="28" t="s">
         <v>723</v>
       </c>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E145" s="31"/>
     </row>
-    <row r="146" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A146" s="28" t="s">
         <v>726</v>
       </c>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="E146" s="31"/>
     </row>
-    <row r="147" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="28" t="s">
         <v>729</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="28" t="s">
         <v>733</v>
       </c>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="E148" s="31"/>
     </row>
-    <row r="149" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A149" s="28" t="s">
         <v>736</v>
       </c>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="E149" s="31"/>
     </row>
-    <row r="150" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A150" s="28" t="s">
         <v>740</v>
       </c>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E150" s="31"/>
     </row>
-    <row r="151" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A151" s="28" t="s">
         <v>743</v>
       </c>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="E151" s="31"/>
     </row>
-    <row r="152" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A152" s="28" t="s">
         <v>746</v>
       </c>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="E152" s="31"/>
     </row>
-    <row r="153" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A153" s="28" t="s">
         <v>749</v>
       </c>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="E153" s="31"/>
     </row>
-    <row r="154" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="30" t="s">
         <v>752</v>
       </c>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E154" s="31"/>
     </row>
-    <row r="155" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="30" t="s">
         <v>756</v>
       </c>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E155" s="31"/>
     </row>
-    <row r="156" spans="1:5" ht="76" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A156" s="30" t="s">
         <v>759</v>
       </c>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="E156" s="31"/>
     </row>
-    <row r="157" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="30" t="s">
         <v>763</v>
       </c>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E157" s="31"/>
     </row>
-    <row r="158" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A158" s="28" t="s">
         <v>766</v>
       </c>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="E158" s="29"/>
     </row>
-    <row r="159" spans="1:5" ht="26" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A159" s="28" t="s">
         <v>770</v>
       </c>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E159" s="29"/>
     </row>
-    <row r="160" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="28" t="s">
         <v>773</v>
       </c>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E160" s="29"/>
     </row>
-    <row r="161" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A161" s="28" t="s">
         <v>776</v>
       </c>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="E161" s="40"/>
     </row>
-    <row r="162" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="28" t="s">
         <v>780</v>
       </c>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="E162" s="40"/>
     </row>
-    <row r="163" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="28" t="s">
         <v>783</v>
       </c>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E163" s="40"/>
     </row>
-    <row r="164" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="28" t="s">
         <v>787</v>
       </c>
@@ -12292,7 +12292,7 @@
       <c r="D164" s="6"/>
       <c r="E164" s="40"/>
     </row>
-    <row r="165" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A165" s="41" t="s">
         <v>789</v>
       </c>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="E165" s="40"/>
     </row>
-    <row r="166" spans="1:5" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A166" s="41" t="s">
         <v>792</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A167" s="41" t="s">
         <v>796</v>
       </c>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="E167" s="40"/>
     </row>
-    <row r="168" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A168" s="41" t="s">
         <v>799</v>
       </c>
@@ -12352,7 +12352,7 @@
       <c r="D168" s="25"/>
       <c r="E168" s="40"/>
     </row>
-    <row r="169" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A169" s="41" t="s">
         <v>800</v>
       </c>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="E169" s="40"/>
     </row>
-    <row r="170" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A170" s="41" t="s">
         <v>803</v>
       </c>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="E170" s="43"/>
     </row>
-    <row r="171" spans="1:5" ht="88" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A171" s="41" t="s">
         <v>807</v>
       </c>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="E171" s="43"/>
     </row>
-    <row r="172" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="44" t="s">
         <v>810</v>
       </c>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="E172" s="40"/>
     </row>
-    <row r="173" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="44" t="s">
         <v>813</v>
       </c>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="E173" s="40"/>
     </row>
-    <row r="174" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="28" t="s">
         <v>816</v>
       </c>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="E174" s="29"/>
     </row>
-    <row r="175" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A175" s="28" t="s">
         <v>819</v>
       </c>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="E175" s="29"/>
     </row>
-    <row r="176" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="28" t="s">
         <v>821</v>
       </c>
@@ -12470,7 +12470,7 @@
       <c r="D176" s="6"/>
       <c r="E176" s="29"/>
     </row>
-    <row r="177" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A177" s="28" t="s">
         <v>823</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A178" s="28" t="s">
         <v>827</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="28" t="s">
         <v>831</v>
       </c>
@@ -12519,7 +12519,7 @@
       </c>
       <c r="E179" s="29"/>
     </row>
-    <row r="180" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="28" t="s">
         <v>834</v>
       </c>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="E180" s="29"/>
     </row>
-    <row r="181" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="28" t="s">
         <v>837</v>
       </c>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E181" s="29"/>
     </row>
-    <row r="182" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A182" s="28" t="s">
         <v>840</v>
       </c>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="E182" s="29"/>
     </row>
-    <row r="183" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A183" s="28" t="s">
         <v>843</v>
       </c>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="E183" s="29"/>
     </row>
-    <row r="184" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A184" s="28" t="s">
         <v>846</v>
       </c>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="E184" s="29"/>
     </row>
-    <row r="185" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="28" t="s">
         <v>850</v>
       </c>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="E185" s="29"/>
     </row>
-    <row r="186" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="28" t="s">
         <v>853</v>
       </c>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="E186" s="29"/>
     </row>
-    <row r="187" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A187" s="28" t="s">
         <v>856</v>
       </c>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="E187" s="29"/>
     </row>
-    <row r="188" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="28" t="s">
         <v>859</v>
       </c>
@@ -12652,7 +12652,7 @@
       <c r="D188" s="6"/>
       <c r="E188" s="29"/>
     </row>
-    <row r="189" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="28" t="s">
         <v>862</v>
       </c>
@@ -12665,7 +12665,7 @@
       <c r="D189" s="6"/>
       <c r="E189" s="29"/>
     </row>
-    <row r="190" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="28" t="s">
         <v>864</v>
       </c>
@@ -12678,7 +12678,7 @@
       <c r="D190" s="6"/>
       <c r="E190" s="29"/>
     </row>
-    <row r="191" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="28" t="s">
         <v>866</v>
       </c>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="E191" s="36"/>
     </row>
-    <row r="192" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="28" t="s">
         <v>869</v>
       </c>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="E192" s="36"/>
     </row>
-    <row r="193" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="28" t="s">
         <v>871</v>
       </c>
@@ -12721,7 +12721,7 @@
       <c r="D193" s="6"/>
       <c r="E193" s="29"/>
     </row>
-    <row r="194" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="28" t="s">
         <v>873</v>
       </c>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="E194" s="36"/>
     </row>
-    <row r="195" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="28" t="s">
         <v>875</v>
       </c>
@@ -12749,7 +12749,7 @@
       <c r="D195" s="6"/>
       <c r="E195" s="29"/>
     </row>
-    <row r="196" spans="1:5" ht="100" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A196" s="28" t="s">
         <v>876</v>
       </c>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E196" s="29"/>
     </row>
-    <row r="197" spans="1:5" ht="75.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A197" s="28" t="s">
         <v>880</v>
       </c>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="E197" s="29"/>
     </row>
-    <row r="198" spans="1:5" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A198" s="28" t="s">
         <v>883</v>
       </c>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="E198" s="29"/>
     </row>
-    <row r="199" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="28" t="s">
         <v>886</v>
       </c>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E199" s="29"/>
     </row>
-    <row r="200" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="28" t="s">
         <v>889</v>
       </c>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="E200" s="29"/>
     </row>
-    <row r="201" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="28" t="s">
         <v>892</v>
       </c>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="E201" s="29"/>
     </row>
-    <row r="202" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A202" s="28" t="s">
         <v>895</v>
       </c>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="E202" s="29"/>
     </row>
-    <row r="203" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A203" s="28" t="s">
         <v>899</v>
       </c>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="E203" s="29"/>
     </row>
-    <row r="204" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A204" s="28" t="s">
         <v>902</v>
       </c>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E204" s="29"/>
     </row>
-    <row r="205" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="28" t="s">
         <v>905</v>
       </c>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="E205" s="29"/>
     </row>
-    <row r="206" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="28" t="s">
         <v>906</v>
       </c>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="E206" s="29"/>
     </row>
-    <row r="207" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="28" t="s">
         <v>907</v>
       </c>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="E207" s="29"/>
     </row>
-    <row r="208" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="28" t="s">
         <v>909</v>
       </c>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="E208" s="29"/>
     </row>
-    <row r="209" spans="1:5" ht="88.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A209" s="28" t="s">
         <v>910</v>
       </c>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="E209" s="29"/>
     </row>
-    <row r="210" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="30" t="s">
         <v>913</v>
       </c>
@@ -12972,21 +12972,21 @@
       <c r="D210" s="16"/>
       <c r="E210" s="46"/>
     </row>
-    <row r="211" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="30"/>
       <c r="B211" s="16"/>
       <c r="C211" s="17"/>
       <c r="D211" s="16"/>
       <c r="E211" s="46"/>
     </row>
-    <row r="212" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="30"/>
       <c r="B212" s="16"/>
       <c r="C212" s="17"/>
       <c r="D212" s="16"/>
       <c r="E212" s="46"/>
     </row>
-    <row r="213" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="30"/>
       <c r="B213" s="16"/>
       <c r="C213" s="17"/>
@@ -13005,14 +13005,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.81640625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>915</v>
       </c>
@@ -13023,14 +13023,14 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="81" t="s">
         <v>917</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
-    <row r="3" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>16</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <v>16</v>
       </c>
@@ -13063,7 +13063,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <v>16</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <v>16</v>
       </c>
@@ -13085,32 +13085,32 @@
         <v>921</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
     </row>
-    <row r="10" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
     </row>
-    <row r="11" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
     </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -13130,14 +13130,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C147"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.7265625" customWidth="1"/>
-    <col min="2" max="2" width="33.453125" customWidth="1"/>
-    <col min="3" max="3" width="91.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" customWidth="1"/>
+    <col min="3" max="3" width="91.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>922</v>
       </c>
@@ -13148,14 +13148,14 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="83" t="s">
         <v>924</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
-    <row r="3" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>0</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="48">
         <v>128</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <v>150</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="34">
         <v>151</v>
       </c>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C6" s="35"/>
     </row>
-    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="34">
         <v>152</v>
       </c>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="C7" s="35"/>
     </row>
-    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>153</v>
       </c>
@@ -13223,7 +13223,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="34">
         <v>169</v>
       </c>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C9" s="35"/>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="34">
         <v>171</v>
       </c>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="C10" s="35"/>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="34">
         <v>172</v>
       </c>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="C11" s="35"/>
     </row>
-    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="34">
         <v>173</v>
       </c>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="C12" s="35"/>
     </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="48">
         <v>256</v>
       </c>
@@ -13275,7 +13275,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="34">
         <v>276</v>
       </c>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="C14" s="35"/>
     </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="34">
         <v>277</v>
       </c>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="C15" s="35"/>
     </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="34">
         <v>333</v>
       </c>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="C16" s="35"/>
     </row>
-    <row r="17" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="34">
         <v>339</v>
       </c>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="C17" s="35"/>
     </row>
-    <row r="18" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>386</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="34">
         <v>387</v>
       </c>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C19" s="35"/>
     </row>
-    <row r="20" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="34">
         <v>388</v>
       </c>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="C20" s="35"/>
     </row>
-    <row r="21" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="34">
         <v>389</v>
       </c>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="C21" s="35"/>
     </row>
-    <row r="22" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="34">
         <v>390</v>
       </c>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="C22" s="35"/>
     </row>
-    <row r="23" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="14">
         <v>527</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="34">
         <v>528</v>
       </c>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="C24" s="35"/>
     </row>
-    <row r="25" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="34">
         <v>532</v>
       </c>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="C25" s="35"/>
     </row>
-    <row r="26" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="14">
         <v>537</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="34">
         <v>1024</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="14">
         <v>1025</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="14">
         <v>1026</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="34">
         <v>1029</v>
       </c>
@@ -13457,7 +13457,7 @@
       </c>
       <c r="C30" s="35"/>
     </row>
-    <row r="31" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="34">
         <v>1044</v>
       </c>
@@ -13469,7 +13469,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="34">
         <v>1063</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="34">
         <v>1152</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="34">
         <v>1153</v>
       </c>
@@ -13505,7 +13505,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="34">
         <v>1174</v>
       </c>
@@ -13517,7 +13517,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="34">
         <v>1175</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="34">
         <v>1177</v>
       </c>
@@ -13541,7 +13541,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="34">
         <v>1195</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="34">
         <v>1197</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="34">
         <v>1280</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="34">
         <v>1300</v>
       </c>
@@ -13589,7 +13589,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="14">
         <v>1363</v>
       </c>
@@ -13601,7 +13601,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="34">
         <v>1551</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="34">
         <v>1556</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="34">
         <v>1557</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="34">
         <v>1561</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="34">
         <v>2049</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="48">
         <v>2176</v>
       </c>
@@ -13673,7 +13673,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="34">
         <v>2199</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="34">
         <v>2219</v>
       </c>
@@ -13697,7 +13697,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="34">
         <v>2221</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="48">
         <v>2304</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="34">
         <v>2324</v>
       </c>
@@ -13733,7 +13733,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="14">
         <v>2434</v>
       </c>
@@ -13745,7 +13745,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="14">
         <v>2437</v>
       </c>
@@ -13757,7 +13757,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="34">
         <v>2580</v>
       </c>
@@ -13769,7 +13769,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="34">
         <v>2585</v>
       </c>
@@ -13781,7 +13781,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="14">
         <v>4224</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="14">
         <v>6876</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="34">
         <v>9119</v>
       </c>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="C60" s="35"/>
     </row>
-    <row r="61" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="14">
         <v>10240</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="34">
         <v>12282</v>
       </c>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="C62" s="35"/>
     </row>
-    <row r="63" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="34">
         <v>13312</v>
       </c>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C63" s="35"/>
     </row>
-    <row r="64" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="34">
         <v>14464</v>
       </c>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="C64" s="35"/>
     </row>
-    <row r="65" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="14">
         <v>16383</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="34">
         <v>16512</v>
       </c>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="C66" s="35"/>
     </row>
-    <row r="67" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="34">
         <v>16514</v>
       </c>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C67" s="35"/>
     </row>
-    <row r="68" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="34">
         <v>16534</v>
       </c>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="C68" s="35"/>
     </row>
-    <row r="69" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="34">
         <v>16535</v>
       </c>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="C69" s="35"/>
     </row>
-    <row r="70" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="34">
         <v>16640</v>
       </c>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="C70" s="35"/>
     </row>
-    <row r="71" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="34">
         <v>16661</v>
       </c>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C71" s="35"/>
     </row>
-    <row r="72" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="34">
         <v>16770</v>
       </c>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="C72" s="35"/>
     </row>
-    <row r="73" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="34">
         <v>16773</v>
       </c>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="C73" s="35"/>
     </row>
-    <row r="74" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="34">
         <v>16832</v>
       </c>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C74" s="35"/>
     </row>
-    <row r="75" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="34">
         <v>16916</v>
       </c>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="C75" s="35"/>
     </row>
-    <row r="76" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="34">
         <v>16921</v>
       </c>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="C76" s="35"/>
     </row>
-    <row r="77" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="34">
         <v>17409</v>
       </c>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="C77" s="35"/>
     </row>
-    <row r="78" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="34">
         <v>17410</v>
       </c>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="C78" s="35"/>
     </row>
-    <row r="79" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="34">
         <v>17536</v>
       </c>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="C79" s="35"/>
     </row>
-    <row r="80" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="34">
         <v>17558</v>
       </c>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="C80" s="35"/>
     </row>
-    <row r="81" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="34">
         <v>17945</v>
       </c>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="C81" s="35"/>
     </row>
-    <row r="82" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="34">
         <v>18560</v>
       </c>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C82" s="35"/>
     </row>
-    <row r="83" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="34">
         <v>18708</v>
       </c>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C83" s="35"/>
     </row>
-    <row r="84" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="34">
         <v>18818</v>
       </c>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="C84" s="35"/>
     </row>
-    <row r="85" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="34">
         <v>18969</v>
       </c>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="C85" s="35"/>
     </row>
-    <row r="86" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="14">
         <v>23260</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="14">
         <v>32896</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="34">
         <v>32918</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="14">
         <v>32921</v>
       </c>
@@ -14117,7 +14117,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="34">
         <v>33044</v>
       </c>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="C90" s="35"/>
     </row>
-    <row r="91" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="34">
         <v>33107</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="34">
         <v>33154</v>
       </c>
@@ -14151,7 +14151,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="34">
         <v>33157</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="34">
         <v>33300</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="34">
         <v>33305</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="34">
         <v>33793</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="34">
         <v>33794</v>
       </c>
@@ -14211,7 +14211,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="14">
         <v>33921</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="34">
         <v>33943</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="34">
         <v>34319</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="34">
         <v>34329</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="14">
         <v>39644</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="34">
         <v>49280</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="34">
         <v>49302</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="34">
         <v>49538</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="34">
         <v>49541</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="34">
         <v>49689</v>
       </c>
@@ -14331,7 +14331,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="34">
         <v>50177</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="14">
         <v>56028</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="34">
         <v>67584</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="34">
         <v>67840</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="34">
         <v>131604</v>
       </c>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="C112" s="35"/>
     </row>
-    <row r="113" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="34">
         <v>132097</v>
       </c>
@@ -14399,7 +14399,7 @@
       </c>
       <c r="C113" s="35"/>
     </row>
-    <row r="114" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="34">
         <v>262272</v>
       </c>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="C114" s="35"/>
     </row>
-    <row r="115" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="34">
         <v>262533</v>
       </c>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="C115" s="35"/>
     </row>
-    <row r="116" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="34">
         <v>262676</v>
       </c>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="C116" s="35"/>
     </row>
-    <row r="117" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="34">
         <v>262681</v>
       </c>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="C117" s="35"/>
     </row>
-    <row r="118" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="34">
         <v>524416</v>
       </c>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="C118" s="35"/>
     </row>
-    <row r="119" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="34">
         <v>524674</v>
       </c>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C119" s="35"/>
     </row>
-    <row r="120" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="34">
         <v>524675</v>
       </c>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="C120" s="35"/>
     </row>
-    <row r="121" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="34">
         <v>524677</v>
       </c>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="C121" s="35"/>
     </row>
-    <row r="122" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="34">
         <v>524820</v>
       </c>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="C122" s="35"/>
     </row>
-    <row r="123" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="34">
         <v>524825</v>
       </c>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="C123" s="35"/>
     </row>
-    <row r="124" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="34">
         <v>525313</v>
       </c>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="C124" s="35"/>
     </row>
-    <row r="125" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="34">
         <v>525314</v>
       </c>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="C125" s="35"/>
     </row>
-    <row r="126" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="34">
         <v>525315</v>
       </c>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="C126" s="35"/>
     </row>
-    <row r="127" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="34">
         <v>525844</v>
       </c>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="C127" s="35"/>
     </row>
-    <row r="128" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="34">
         <v>540800</v>
       </c>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="C128" s="35"/>
     </row>
-    <row r="129" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="34">
         <v>540825</v>
       </c>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="C129" s="35"/>
     </row>
-    <row r="130" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="34">
         <v>541058</v>
       </c>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="C130" s="35"/>
     </row>
-    <row r="131" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="34">
         <v>541209</v>
       </c>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="C131" s="35"/>
     </row>
-    <row r="132" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="34">
         <v>541697</v>
       </c>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="C132" s="35"/>
     </row>
-    <row r="133" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="34">
         <v>542233</v>
       </c>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="C133" s="35"/>
     </row>
-    <row r="134" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="34">
         <v>542848</v>
       </c>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="C134" s="35"/>
     </row>
-    <row r="135" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="14">
         <v>543106</v>
       </c>
@@ -14621,7 +14621,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="34">
         <v>543257</v>
       </c>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="C136" s="35"/>
     </row>
-    <row r="137" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="14">
         <v>547548</v>
       </c>
@@ -14643,7 +14643,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="34">
         <v>558617</v>
       </c>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="C138" s="35"/>
     </row>
-    <row r="139" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="14">
         <v>573568</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="34">
         <v>573593</v>
       </c>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C140" s="35"/>
     </row>
-    <row r="141" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="34">
         <v>4194432</v>
       </c>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="C141" s="35"/>
     </row>
-    <row r="142" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="34">
         <v>4194454</v>
       </c>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C142" s="35"/>
     </row>
-    <row r="143" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="34">
         <v>4194690</v>
       </c>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="C143" s="35"/>
     </row>
-    <row r="144" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="34">
         <v>4194841</v>
       </c>
@@ -14715,7 +14715,7 @@
       </c>
       <c r="C144" s="35"/>
     </row>
-    <row r="145" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="34">
         <v>4195329</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="C145" s="35"/>
     </row>
-    <row r="146" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="34">
         <v>4196503</v>
       </c>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C146" s="35"/>
     </row>
-    <row r="147" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="34">
         <v>4196523</v>
       </c>
@@ -14760,14 +14760,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="3" width="39.453125" customWidth="1"/>
-    <col min="4" max="4" width="54.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="3" width="39.42578125" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>922</v>
       </c>
@@ -14781,7 +14781,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>336</v>
       </c>
@@ -14791,7 +14791,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -14817,7 +14817,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>16</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>64</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>65</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>67</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>71</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>80</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>81</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>88</v>
       </c>
@@ -14921,7 +14921,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>192</v>
       </c>
@@ -14933,7 +14933,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>193</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>208</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>256</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>257</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>259</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>263</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>272</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>273</v>
       </c>
@@ -15035,7 +15035,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>320</v>
       </c>
@@ -15047,7 +15047,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>321</v>
       </c>
@@ -15059,7 +15059,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>464</v>
       </c>
@@ -15083,14 +15083,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="4" max="4" width="43.1796875" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" customWidth="1"/>
     <col min="11" max="11" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
         <v>978</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
         <v>987</v>
       </c>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K2" s="56"/>
     </row>
-    <row r="3" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57"/>
       <c r="B3" s="55" t="s">
         <v>990</v>
@@ -15175,7 +15175,7 @@
       <c r="J3" s="58"/>
       <c r="K3" s="56"/>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>992</v>
       </c>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="K4" s="56"/>
     </row>
-    <row r="5" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="57"/>
       <c r="B5" s="55" t="s">
         <v>1000</v>
@@ -15225,7 +15225,7 @@
       <c r="J5" s="56"/>
       <c r="K5" s="56"/>
     </row>
-    <row r="6" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="57"/>
       <c r="B6" s="55" t="s">
         <v>1002</v>
@@ -15242,7 +15242,7 @@
       <c r="J6" s="56"/>
       <c r="K6" s="56"/>
     </row>
-    <row r="7" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57"/>
       <c r="B7" s="55" t="s">
         <v>1004</v>
@@ -15259,7 +15259,7 @@
       <c r="J7" s="56"/>
       <c r="K7" s="56"/>
     </row>
-    <row r="8" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="57"/>
       <c r="B8" s="55" t="s">
         <v>1006</v>
@@ -15276,7 +15276,7 @@
       <c r="J8" s="56"/>
       <c r="K8" s="56"/>
     </row>
-    <row r="9" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A9" s="57"/>
       <c r="B9" s="55" t="s">
         <v>1008</v>
@@ -15293,7 +15293,7 @@
       <c r="J9" s="56"/>
       <c r="K9" s="56"/>
     </row>
-    <row r="10" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A10" s="57"/>
       <c r="B10" s="55" t="s">
         <v>1010</v>
@@ -15312,7 +15312,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="54" t="s">
         <v>1013</v>
       </c>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="K11" s="56"/>
     </row>
-    <row r="12" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A12" s="57"/>
       <c r="B12" s="55" t="s">
         <v>1017</v>
@@ -15362,7 +15362,7 @@
       <c r="J12" s="56"/>
       <c r="K12" s="56"/>
     </row>
-    <row r="13" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A13" s="57"/>
       <c r="B13" s="55" t="s">
         <v>1019</v>
@@ -15379,7 +15379,7 @@
       <c r="J13" s="56"/>
       <c r="K13" s="56"/>
     </row>
-    <row r="14" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A14" s="57"/>
       <c r="B14" s="55" t="s">
         <v>1021</v>
@@ -15396,7 +15396,7 @@
       <c r="J14" s="56"/>
       <c r="K14" s="56"/>
     </row>
-    <row r="15" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A15" s="57"/>
       <c r="B15" s="55" t="s">
         <v>1023</v>
@@ -15413,7 +15413,7 @@
       <c r="J15" s="56"/>
       <c r="K15" s="56"/>
     </row>
-    <row r="16" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A16" s="63" t="s">
         <v>1025</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A17" s="57"/>
       <c r="B17" s="55" t="s">
         <v>1030</v>
@@ -15465,7 +15465,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="54" t="s">
         <v>1032</v>
       </c>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="K18" s="56"/>
     </row>
-    <row r="19" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="57"/>
       <c r="B19" s="55" t="s">
         <v>1035</v>
@@ -15515,7 +15515,7 @@
       <c r="J19" s="56"/>
       <c r="K19" s="56"/>
     </row>
-    <row r="20" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A20" s="57"/>
       <c r="B20" s="55" t="s">
         <v>1037</v>
@@ -15532,7 +15532,7 @@
       <c r="J20" s="56"/>
       <c r="K20" s="56"/>
     </row>
-    <row r="21" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A21" s="57"/>
       <c r="B21" s="55" t="s">
         <v>1039</v>
@@ -15549,7 +15549,7 @@
       <c r="J21" s="56"/>
       <c r="K21" s="56"/>
     </row>
-    <row r="22" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A22" s="57"/>
       <c r="B22" s="55" t="s">
         <v>1041</v>
@@ -15566,7 +15566,7 @@
       <c r="J22" s="56"/>
       <c r="K22" s="56"/>
     </row>
-    <row r="23" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A23" s="63" t="s">
         <v>1043</v>
       </c>
@@ -15599,7 +15599,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A24" s="57"/>
       <c r="B24" s="23">
         <v>8389906</v>
@@ -15618,7 +15618,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A25" s="57"/>
       <c r="B25" s="23">
         <v>10487058</v>
@@ -15635,7 +15635,7 @@
       <c r="J25" s="56"/>
       <c r="K25" s="56"/>
     </row>
-    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A26" s="54" t="s">
         <v>1048</v>
       </c>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="K26" s="56"/>
     </row>
-    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" s="54" t="s">
         <v>1052</v>
       </c>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="K27" s="56"/>
     </row>
-    <row r="28" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A28" s="57"/>
       <c r="B28" s="55" t="s">
         <v>1056</v>
@@ -15718,7 +15718,7 @@
       <c r="J28" s="56"/>
       <c r="K28" s="56"/>
     </row>
-    <row r="29" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A29" s="57"/>
       <c r="B29" s="55" t="s">
         <v>1058</v>
@@ -15735,7 +15735,7 @@
       <c r="J29" s="56"/>
       <c r="K29" s="56"/>
     </row>
-    <row r="30" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="54" t="s">
         <v>1060</v>
       </c>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="K30" s="56"/>
     </row>
-    <row r="31" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A31" s="57"/>
       <c r="B31" s="55" t="s">
         <v>1065</v>
@@ -15785,7 +15785,7 @@
       <c r="J31" s="56"/>
       <c r="K31" s="56"/>
     </row>
-    <row r="32" spans="1:11" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A32" s="57"/>
       <c r="B32" s="55" t="s">
         <v>1067</v>
@@ -15802,7 +15802,7 @@
       <c r="J32" s="56"/>
       <c r="K32" s="56"/>
     </row>
-    <row r="33" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A33" s="54" t="s">
         <v>1069</v>
       </c>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="K33" s="56"/>
     </row>
-    <row r="34" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="54" t="s">
         <v>1074</v>
       </c>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="K34" s="56"/>
     </row>
-    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="54" t="s">
         <v>1078</v>
       </c>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="K35" s="56"/>
     </row>
-    <row r="36" spans="1:11" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A36" s="63" t="s">
         <v>1082</v>
       </c>
@@ -15920,7 +15920,7 @@
       <c r="J36" s="56"/>
       <c r="K36" s="56"/>
     </row>
-    <row r="37" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="54" t="s">
         <v>1084</v>
       </c>
@@ -15965,16 +15965,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="29.81640625" customWidth="1"/>
-    <col min="4" max="4" width="30.81640625" customWidth="1"/>
-    <col min="5" max="5" width="29.7265625" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
         <v>922</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
         <v>1090</v>
       </c>
@@ -16000,7 +16000,7 @@
       <c r="D2" s="82"/>
       <c r="E2" s="82"/>
     </row>
-    <row r="3" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="55">
         <v>2114</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
         <v>1095</v>
       </c>
@@ -16034,7 +16034,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
         <v>1097</v>
       </c>
@@ -16045,7 +16045,7 @@
       <c r="D5" s="58"/>
       <c r="E5" s="58"/>
     </row>
-    <row r="6" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="55">
         <v>10273</v>
       </c>
@@ -16062,7 +16062,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
         <v>1101</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="12.75" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
         <v>1103</v>
       </c>
@@ -16090,7 +16090,7 @@
       <c r="D8" s="58"/>
       <c r="E8" s="58"/>
     </row>
-    <row r="9" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="55" t="s">
         <v>1105</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="55" t="s">
         <v>1108</v>
       </c>
@@ -16124,7 +16124,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>40960</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>51266</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="55" t="s">
         <v>1115</v>
       </c>
@@ -16190,14 +16190,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1117</v>
       </c>
@@ -16211,7 +16211,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="73">
         <v>32768</v>
       </c>
@@ -16226,7 +16226,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="73">
         <f t="shared" ref="A3:A61" si="1">SUM(A2, 1)</f>
         <v>32769</v>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="D3" s="74"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="73">
         <f t="shared" si="1"/>
         <v>32770</v>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="D4" s="74"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="73">
         <f t="shared" si="1"/>
         <v>32771</v>
@@ -16270,7 +16270,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="73">
         <f t="shared" si="1"/>
         <v>32772</v>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="D6" s="74"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="73">
         <f t="shared" si="1"/>
         <v>32773</v>
@@ -16296,7 +16296,7 @@
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="73">
         <f t="shared" si="1"/>
         <v>32774</v>
@@ -16308,7 +16308,7 @@
       <c r="C8" s="74"/>
       <c r="D8" s="74"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="73">
         <f t="shared" si="1"/>
         <v>32775</v>
@@ -16320,7 +16320,7 @@
       <c r="C9" s="74"/>
       <c r="D9" s="74"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="73">
         <f t="shared" si="1"/>
         <v>32776</v>
@@ -16332,7 +16332,7 @@
       <c r="C10" s="74"/>
       <c r="D10" s="74"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="73">
         <f t="shared" si="1"/>
         <v>32777</v>
@@ -16344,7 +16344,7 @@
       <c r="C11" s="74"/>
       <c r="D11" s="74"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="73">
         <f t="shared" si="1"/>
         <v>32778</v>
@@ -16356,7 +16356,7 @@
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="73">
         <f t="shared" si="1"/>
         <v>32779</v>
@@ -16368,7 +16368,7 @@
       <c r="C13" s="74"/>
       <c r="D13" s="74"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="73">
         <f t="shared" si="1"/>
         <v>32780</v>
@@ -16380,7 +16380,7 @@
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="73">
         <f t="shared" si="1"/>
         <v>32781</v>
@@ -16396,7 +16396,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="73">
         <f t="shared" si="1"/>
         <v>32782</v>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="D16" s="74"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="73">
         <f t="shared" si="1"/>
         <v>32783</v>
@@ -16426,7 +16426,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="73">
         <f t="shared" si="1"/>
         <v>32784</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="D18" s="74"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="73">
         <f t="shared" si="1"/>
         <v>32785</v>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D19" s="74"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="73">
         <f t="shared" si="1"/>
         <v>32786</v>
@@ -16466,7 +16466,7 @@
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="73">
         <f t="shared" si="1"/>
         <v>32787</v>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="D21" s="74"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="73">
         <f t="shared" si="1"/>
         <v>32788</v>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="D22" s="74"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="73">
         <f t="shared" si="1"/>
         <v>32789</v>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="D23" s="74"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="73">
         <f t="shared" si="1"/>
         <v>32790</v>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="D24" s="74"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="73">
         <f t="shared" si="1"/>
         <v>32791</v>
@@ -16538,7 +16538,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="73">
         <f t="shared" si="1"/>
         <v>32792</v>
@@ -16554,7 +16554,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="73">
         <f t="shared" si="1"/>
         <v>32793</v>
@@ -16570,7 +16570,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="73">
         <f t="shared" si="1"/>
         <v>32794</v>
@@ -16586,7 +16586,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="73">
         <f t="shared" si="1"/>
         <v>32795</v>
@@ -16602,7 +16602,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="73">
         <f t="shared" si="1"/>
         <v>32796</v>
@@ -16618,7 +16618,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="73">
         <f t="shared" si="1"/>
         <v>32797</v>
@@ -16630,7 +16630,7 @@
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="73">
         <f t="shared" si="1"/>
         <v>32798</v>
@@ -16642,7 +16642,7 @@
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="73">
         <f t="shared" si="1"/>
         <v>32799</v>
@@ -16654,7 +16654,7 @@
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
     </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="73">
         <f t="shared" si="1"/>
         <v>32800</v>
@@ -16666,7 +16666,7 @@
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>
     </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="73">
         <f t="shared" si="1"/>
         <v>32801</v>
@@ -16682,7 +16682,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="73">
         <f t="shared" si="1"/>
         <v>32802</v>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="D36" s="74"/>
     </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="73">
         <f t="shared" si="1"/>
         <v>32803</v>
@@ -16712,7 +16712,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="73">
         <f t="shared" si="1"/>
         <v>32804</v>
@@ -16728,7 +16728,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="73">
         <f t="shared" si="1"/>
         <v>32805</v>
@@ -16744,7 +16744,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="73">
         <f t="shared" si="1"/>
         <v>32806</v>
@@ -16760,7 +16760,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="73">
         <f t="shared" si="1"/>
         <v>32807</v>
@@ -16772,7 +16772,7 @@
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
     </row>
-    <row r="42" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="73">
         <f t="shared" si="1"/>
         <v>32808</v>
@@ -16784,7 +16784,7 @@
       <c r="C42" s="74"/>
       <c r="D42" s="74"/>
     </row>
-    <row r="43" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="73">
         <f t="shared" si="1"/>
         <v>32809</v>
@@ -16796,7 +16796,7 @@
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
     </row>
-    <row r="44" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="73">
         <f t="shared" si="1"/>
         <v>32810</v>
@@ -16808,7 +16808,7 @@
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
     </row>
-    <row r="45" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="73">
         <f t="shared" si="1"/>
         <v>32811</v>
@@ -16820,7 +16820,7 @@
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
     </row>
-    <row r="46" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="73">
         <f t="shared" si="1"/>
         <v>32812</v>
@@ -16832,7 +16832,7 @@
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
     </row>
-    <row r="47" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="73">
         <f t="shared" si="1"/>
         <v>32813</v>
@@ -16844,7 +16844,7 @@
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
     </row>
-    <row r="48" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="73">
         <f t="shared" si="1"/>
         <v>32814</v>
@@ -16856,7 +16856,7 @@
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
     </row>
-    <row r="49" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="73">
         <f t="shared" si="1"/>
         <v>32815</v>
@@ -16868,7 +16868,7 @@
       <c r="C49" s="74"/>
       <c r="D49" s="74"/>
     </row>
-    <row r="50" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="73">
         <f t="shared" si="1"/>
         <v>32816</v>
@@ -16880,7 +16880,7 @@
       <c r="C50" s="74"/>
       <c r="D50" s="74"/>
     </row>
-    <row r="51" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="73">
         <f t="shared" si="1"/>
         <v>32817</v>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="D51" s="74"/>
     </row>
-    <row r="52" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="73">
         <f t="shared" si="1"/>
         <v>32818</v>
@@ -16906,7 +16906,7 @@
       <c r="C52" s="74"/>
       <c r="D52" s="74"/>
     </row>
-    <row r="53" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="73">
         <f t="shared" si="1"/>
         <v>32819</v>
@@ -16918,7 +16918,7 @@
       <c r="C53" s="74"/>
       <c r="D53" s="74"/>
     </row>
-    <row r="54" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="73">
         <f t="shared" si="1"/>
         <v>32820</v>
@@ -16930,7 +16930,7 @@
       <c r="C54" s="74"/>
       <c r="D54" s="74"/>
     </row>
-    <row r="55" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="73">
         <f t="shared" si="1"/>
         <v>32821</v>
@@ -16942,7 +16942,7 @@
       <c r="C55" s="74"/>
       <c r="D55" s="74"/>
     </row>
-    <row r="56" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="73">
         <f t="shared" si="1"/>
         <v>32822</v>
@@ -16954,7 +16954,7 @@
       <c r="C56" s="74"/>
       <c r="D56" s="74"/>
     </row>
-    <row r="57" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="73">
         <f t="shared" si="1"/>
         <v>32823</v>
@@ -16966,7 +16966,7 @@
       <c r="C57" s="74"/>
       <c r="D57" s="74"/>
     </row>
-    <row r="58" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="73">
         <f t="shared" si="1"/>
         <v>32824</v>
@@ -16978,7 +16978,7 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
     </row>
-    <row r="59" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="73">
         <f t="shared" si="1"/>
         <v>32825</v>
@@ -16994,7 +16994,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="73">
         <f t="shared" si="1"/>
         <v>32826</v>
@@ -17006,7 +17006,7 @@
       <c r="C60" s="74"/>
       <c r="D60" s="74"/>
     </row>
-    <row r="61" spans="1:4" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="73">
         <f t="shared" si="1"/>
         <v>32827</v>
@@ -17031,13 +17031,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.81640625" customWidth="1"/>
-    <col min="2" max="2" width="60.54296875" customWidth="1"/>
+    <col min="1" max="1" width="39.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="75" t="s">
         <v>1161</v>
       </c>
@@ -17045,13 +17045,13 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
         <v>1162</v>
       </c>
       <c r="B2" s="82"/>
     </row>
-    <row r="3" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
         <v>1163</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
         <v>329</v>
       </c>
@@ -17067,7 +17067,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
         <v>332</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
         <v>335</v>
       </c>
@@ -17083,7 +17083,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
         <v>338</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
         <v>341</v>
       </c>
@@ -17099,7 +17099,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
         <v>345</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
         <v>368</v>
       </c>
@@ -17115,7 +17115,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
         <v>1170</v>
       </c>
@@ -17123,7 +17123,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
         <v>1172</v>
       </c>
@@ -17131,31 +17131,31 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="85" t="s">
         <v>1174</v>
       </c>
       <c r="B13" s="82"/>
     </row>
-    <row r="14" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="86" t="s">
         <v>1175</v>
       </c>
       <c r="B14" s="82"/>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="85" t="s">
         <v>1176</v>
       </c>
       <c r="B15" s="82"/>
     </row>
-    <row r="16" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="86" t="s">
         <v>1177</v>
       </c>
       <c r="B16" s="82"/>
     </row>
-    <row r="17" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
         <v>327</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
         <v>1179</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
         <v>1181</v>
       </c>
@@ -17179,7 +17179,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
         <v>1183</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17195,7 +17195,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17203,7 +17203,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17211,7 +17211,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="23" t="s">
         <v>1191</v>
       </c>
@@ -17219,7 +17219,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="23" t="s">
         <v>1193</v>
       </c>
@@ -17227,7 +17227,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="23" t="s">
         <v>1195</v>
       </c>
@@ -17235,19 +17235,19 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="85" t="s">
         <v>1197</v>
       </c>
       <c r="B27" s="82"/>
     </row>
-    <row r="28" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="86" t="s">
         <v>1198</v>
       </c>
       <c r="B28" s="82"/>
     </row>
-    <row r="29" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="23" t="s">
         <v>1199</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="23" t="s">
         <v>1201</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="23" t="s">
         <v>1203</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="23" t="s">
         <v>1205</v>
       </c>
@@ -17279,13 +17279,13 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="85" t="s">
         <v>1207</v>
       </c>
       <c r="B33" s="82"/>
     </row>
-    <row r="34" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
         <v>327</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="76" t="s">
         <v>1209</v>
       </c>
@@ -17301,7 +17301,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="76" t="s">
         <v>1179</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="23" t="s">
         <v>1212</v>
       </c>
@@ -17317,7 +17317,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="76" t="s">
         <v>1181</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="23" t="s">
         <v>1215</v>
       </c>
@@ -17333,7 +17333,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="23" t="s">
         <v>1217</v>
       </c>
@@ -17341,7 +17341,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
         <v>1219</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="76" t="s">
         <v>1183</v>
       </c>
@@ -17357,7 +17357,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="23" t="s">
         <v>1222</v>
       </c>
@@ -17365,7 +17365,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="23" t="s">
         <v>1224</v>
       </c>
@@ -17373,7 +17373,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="23" t="s">
         <v>1226</v>
       </c>
@@ -17381,7 +17381,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="23" t="s">
         <v>1228</v>
       </c>
@@ -17389,7 +17389,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
         <v>1230</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="23" t="s">
         <v>1232</v>
       </c>
@@ -17405,7 +17405,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="23" t="s">
         <v>1234</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17429,7 +17429,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17437,13 +17437,13 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A53" s="85" t="s">
         <v>1239</v>
       </c>
       <c r="B53" s="82"/>
     </row>
-    <row r="54" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="23" t="s">
         <v>327</v>
       </c>
@@ -17451,7 +17451,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="76" t="s">
         <v>1179</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="76" t="s">
         <v>1181</v>
       </c>
@@ -17467,7 +17467,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="23" t="s">
         <v>1217</v>
       </c>
@@ -17475,7 +17475,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="76" t="s">
         <v>1183</v>
       </c>
@@ -17483,7 +17483,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="23" t="s">
         <v>1224</v>
       </c>
@@ -17491,7 +17491,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="23" t="s">
         <v>1228</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="23" t="s">
         <v>1232</v>
       </c>
@@ -17507,7 +17507,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="76" t="s">
         <v>1185</v>
       </c>
@@ -17515,7 +17515,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="23" t="s">
         <v>1249</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="23" t="s">
         <v>1251</v>
       </c>
@@ -17531,7 +17531,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="23" t="s">
         <v>1253</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="23" t="s">
         <v>1255</v>
       </c>
@@ -17547,7 +17547,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="23" t="s">
         <v>1257</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="23" t="s">
         <v>1259</v>
       </c>
@@ -17563,7 +17563,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="23" t="s">
         <v>1261</v>
       </c>
@@ -17571,13 +17571,13 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A70" s="85" t="s">
         <v>1263</v>
       </c>
       <c r="B70" s="82"/>
     </row>
-    <row r="71" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="23" t="s">
         <v>327</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="23" t="s">
         <v>1181</v>
       </c>
@@ -17593,7 +17593,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="23" t="s">
         <v>1183</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="23" t="s">
         <v>1185</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17617,13 +17617,13 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="85" t="s">
         <v>1269</v>
       </c>
       <c r="B76" s="82"/>
     </row>
-    <row r="77" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="23" t="s">
         <v>327</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="23" t="s">
         <v>1187</v>
       </c>
@@ -17639,7 +17639,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="23" t="s">
         <v>1189</v>
       </c>
@@ -17647,7 +17647,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="23" t="s">
         <v>1191</v>
       </c>
